--- a/projects/P_300_Vantage_Point_Pattern_Recognition/data/live/History Grid (EXP).xlsx
+++ b/projects/P_300_Vantage_Point_Pattern_Recognition/data/live/History Grid (EXP).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="27">
   <si>
     <t>High
 Price</t>
@@ -67,11 +67,11 @@
 Price</t>
   </si>
   <si>
+    <t>Medium</t>
+  </si>
+  <si>
     <t>Low
 Price</t>
-  </si>
-  <si>
-    <t>Triple Cross Medium</t>
   </si>
   <si>
     <t>Long
@@ -81,6 +81,9 @@
   <si>
     <t>Close
 Price</t>
+  </si>
+  <si>
+    <t>Long</t>
   </si>
   <si>
     <t>Predicted
@@ -93,6 +96,9 @@
 Difference</t>
   </si>
   <si>
+    <t>Short</t>
+  </si>
+  <si>
     <t>Volume</t>
   </si>
   <si>
@@ -102,17 +108,11 @@
     <t>ROC%</t>
   </si>
   <si>
-    <t>Triple Cross Short</t>
-  </si>
-  <si>
     <t>Williams
 EMAI</t>
   </si>
   <si>
     <t>Neural Index</t>
-  </si>
-  <si>
-    <t>Triple Cross Long</t>
   </si>
 </sst>
 </file>
@@ -150,10 +150,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" readingOrder="0"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -466,9 +466,9 @@
     <col min="14" max="14" width="17.28515625" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" customWidth="1"/>
     <col min="16" max="16" width="17.7109375" customWidth="1"/>
-    <col min="17" max="17" width="23.7109375" customWidth="1"/>
-    <col min="18" max="18" width="27" customWidth="1"/>
-    <col min="19" max="19" width="23.28515625" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="22" width="14.5703125" customWidth="1"/>
     <col min="23" max="16384" width="8.7265625"/>
   </cols>
@@ -477,74 +477,74 @@
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="M1" t="s">
         <v>9</v>
       </c>
       <c r="O1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q1" t="s">
         <v>3</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="L2" s="2"/>
       <c r="M2" t="s">
         <v>4</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O2" t="s">
         <v>10</v>
@@ -553,2872 +553,2804 @@
         <v>8</v>
       </c>
       <c r="Q2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="2">
-        <v>46227</v>
+      <c r="A3" s="1">
+        <v>46237</v>
       </c>
       <c r="B3">
-        <v>4.06655883789063</v>
+        <v>-0.233200073242188</v>
       </c>
       <c r="C3">
-        <v>1.94187927246094</v>
+        <v>0.889419555664063</v>
       </c>
       <c r="D3">
-        <v>-0.0666046142578125</v>
+        <v>1.60643005371094</v>
       </c>
       <c r="E3">
-        <v>208.380004882813</v>
+        <v>207.089996337891</v>
       </c>
       <c r="F3">
-        <v>213.690002441406</v>
+        <v>214.880004882813</v>
       </c>
       <c r="G3">
-        <v>205.800003051758</v>
+        <v>207.089996337891</v>
       </c>
       <c r="H3">
-        <v>213.550003051758</v>
+        <v>214.740005493164</v>
       </c>
       <c r="I3">
-        <v>214.368743896484</v>
+        <v>217.553192138672</v>
       </c>
       <c r="J3">
-        <v>210.048736572266</v>
+        <v>209.957611083984</v>
       </c>
       <c r="K3">
-        <v>485400</v>
+        <v>409500</v>
       </c>
       <c r="L3">
-        <v>-0.859048008918762</v>
+        <v>-0.483808249235153</v>
       </c>
       <c r="M3">
-        <v>31.9946136474609</v>
+        <v>28.9552879333496</v>
       </c>
       <c r="N3">
-        <v>-36.1660003662109</v>
+        <v>-28.3486042022705</v>
       </c>
       <c r="O3" t="s">
         <v>1</v>
       </c>
       <c r="P3">
-        <v>56.1674270629883</v>
+        <v>66.263298034668</v>
       </c>
       <c r="Q3">
-        <v>208.829559326172</v>
+        <v>210.392547607422</v>
       </c>
       <c r="R3">
-        <v>207.952407836914</v>
+        <v>210.768096923828</v>
       </c>
       <c r="S3">
-        <v>210.00927734375</v>
+        <v>211.0498046875</v>
       </c>
       <c r="T3">
-        <v>0.678741455078125</v>
+        <v>2.67318725585938</v>
       </c>
       <c r="U3">
-        <v>4.24873352050781</v>
+        <v>2.86761474609375</v>
       </c>
       <c r="V3">
-        <v>4.32000732421875</v>
+        <v>7.5955810546875</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="2">
-        <v>46226</v>
+      <c r="A4" s="1">
+        <v>46234</v>
       </c>
       <c r="B4">
-        <v>0.735427856445313</v>
+        <v>-6.41073608398438</v>
       </c>
       <c r="C4">
-        <v>-1.12678527832031</v>
+        <v>-0.469528198242188</v>
       </c>
       <c r="D4">
-        <v>-2.83802795410156</v>
+        <v>0.9327392578125</v>
       </c>
       <c r="E4">
-        <v>200.570007324219</v>
+        <v>203.770004272461</v>
       </c>
       <c r="F4">
-        <v>207.524993896484</v>
+        <v>211.625</v>
       </c>
       <c r="G4">
-        <v>197.789993286133</v>
+        <v>200.919998168945</v>
       </c>
       <c r="H4">
-        <v>207.110000610352</v>
+        <v>204.940002441406</v>
       </c>
       <c r="I4">
-        <v>209.162963867188</v>
+        <v>207.662490844727</v>
       </c>
       <c r="J4">
-        <v>203.450393676758</v>
+        <v>200.627029418945</v>
       </c>
       <c r="K4">
-        <v>365900</v>
+        <v>641100</v>
       </c>
       <c r="L4">
-        <v>-0.617619812488556</v>
+        <v>-0.915714085102081</v>
       </c>
       <c r="M4">
-        <v>50.1215858459473</v>
+        <v>40.4113388061523</v>
       </c>
       <c r="N4">
-        <v>-27.2684688568115</v>
+        <v>-17.9891490936279</v>
       </c>
       <c r="O4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4">
+        <v>-30.0875549316406</v>
+      </c>
+      <c r="Q4">
+        <v>206.705017089844</v>
+      </c>
+      <c r="R4">
+        <v>209.544830322266</v>
+      </c>
+      <c r="S4">
+        <v>210.678985595703</v>
+      </c>
+      <c r="T4">
+        <v>-3.96250915527344</v>
+      </c>
+      <c r="U4">
+        <v>-0.29296875</v>
+      </c>
+      <c r="V4">
+        <v>7.03546142578125</v>
+      </c>
+    </row>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B5">
+        <v>-6.14503479003906</v>
+      </c>
+      <c r="C5">
+        <v>1.31637573242188</v>
+      </c>
+      <c r="D5">
+        <v>2.18217468261719</v>
+      </c>
+      <c r="E5">
+        <v>211.110000610352</v>
+      </c>
+      <c r="F5">
+        <v>211.110000610352</v>
+      </c>
+      <c r="G5">
+        <v>201.050003051758</v>
+      </c>
+      <c r="H5">
+        <v>205.479995727539</v>
+      </c>
+      <c r="I5">
+        <v>209.684875488281</v>
+      </c>
+      <c r="J5">
+        <v>199.297424316406</v>
+      </c>
+      <c r="K5">
+        <v>644500</v>
+      </c>
+      <c r="L5">
+        <v>-1.1566663980484</v>
+      </c>
+      <c r="M5">
+        <v>49.2756004333496</v>
+      </c>
+      <c r="N5">
+        <v>4.81873273849487</v>
+      </c>
+      <c r="O5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5">
+        <v>-94.0023803710938</v>
+      </c>
+      <c r="Q5">
+        <v>209.008117675781</v>
+      </c>
+      <c r="R5">
+        <v>210.657501220703</v>
+      </c>
+      <c r="S5">
+        <v>211.281936645508</v>
+      </c>
+      <c r="T5">
+        <v>-1.42512512207031</v>
+      </c>
+      <c r="U5">
+        <v>-1.75257873535156</v>
+      </c>
+      <c r="V5">
+        <v>10.387451171875</v>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B6">
+        <v>-1.33183288574219</v>
+      </c>
+      <c r="C6">
+        <v>3.65412902832031</v>
+      </c>
+      <c r="D6">
+        <v>3.998291015625</v>
+      </c>
+      <c r="E6">
+        <v>221.399993896484</v>
+      </c>
+      <c r="F6">
+        <v>221.399993896484</v>
+      </c>
+      <c r="G6">
+        <v>206.115005493164</v>
+      </c>
+      <c r="H6">
+        <v>209.910003662109</v>
+      </c>
+      <c r="I6">
+        <v>212.518249511719</v>
+      </c>
+      <c r="J6">
+        <v>204.73779296875</v>
+      </c>
+      <c r="K6">
+        <v>1127200</v>
+      </c>
+      <c r="L6">
+        <v>-1.06523787975311</v>
+      </c>
+      <c r="M6">
+        <v>47.0102996826172</v>
+      </c>
+      <c r="N6">
+        <v>143.928436279297</v>
+      </c>
+      <c r="O6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6">
+        <v>-94.0882720947266</v>
+      </c>
+      <c r="Q6">
+        <v>213.188323974609</v>
+      </c>
+      <c r="R6">
+        <v>212.123062133789</v>
+      </c>
+      <c r="S6">
+        <v>211.848098754883</v>
+      </c>
+      <c r="T6">
+        <v>-8.88174438476563</v>
+      </c>
+      <c r="U6">
+        <v>-1.37721252441406</v>
+      </c>
+      <c r="V6">
+        <v>7.78045654296875</v>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B7">
+        <v>6.92741394042969</v>
+      </c>
+      <c r="C7">
+        <v>6.81925964355469</v>
+      </c>
+      <c r="D7">
+        <v>5.90208435058594</v>
+      </c>
+      <c r="E7">
+        <v>219.479995727539</v>
+      </c>
+      <c r="F7">
+        <v>225.210006713867</v>
+      </c>
+      <c r="G7">
+        <v>219.095001220703</v>
+      </c>
+      <c r="H7">
+        <v>222.050003051758</v>
+      </c>
+      <c r="I7">
+        <v>224.286346435547</v>
+      </c>
+      <c r="J7">
+        <v>219.966369628906</v>
+      </c>
+      <c r="K7">
+        <v>972400</v>
+      </c>
+      <c r="L7">
+        <v>-0.667619228363037</v>
+      </c>
+      <c r="M7">
+        <v>19.2721691131592</v>
+      </c>
+      <c r="N7">
+        <v>-7.00858736038208</v>
+      </c>
+      <c r="O7" t="s">
         <v>1</v>
       </c>
-      <c r="P4">
-        <v>3.76374173164368</v>
-      </c>
-      <c r="Q4">
-        <v>204.999237060547</v>
-      </c>
-      <c r="R4">
-        <v>206.270782470703</v>
-      </c>
-      <c r="S4">
-        <v>209.638641357422</v>
-      </c>
-      <c r="T4">
-        <v>1.63796997070313</v>
-      </c>
-      <c r="U4">
-        <v>5.660400390625</v>
-      </c>
-      <c r="V4">
-        <v>5.71257019042969</v>
-      </c>
-    </row>
-    <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B5">
-        <v>-3.04449462890625</v>
-      </c>
-      <c r="C5">
-        <v>-1.46490478515625</v>
-      </c>
-      <c r="D5">
-        <v>-3.32414245605469</v>
-      </c>
-      <c r="E5">
-        <v>206.039993286133</v>
-      </c>
-      <c r="F5">
-        <v>209.759994506836</v>
-      </c>
-      <c r="G5">
-        <v>203.139999389648</v>
-      </c>
-      <c r="H5">
-        <v>203.369995117188</v>
-      </c>
-      <c r="I5">
-        <v>205.625869750977</v>
-      </c>
-      <c r="J5">
-        <v>198.4267578125</v>
-      </c>
-      <c r="K5">
-        <v>319800</v>
-      </c>
-      <c r="L5">
-        <v>-0.9128577709198</v>
-      </c>
-      <c r="M5">
-        <v>68.9131469726563</v>
-      </c>
-      <c r="N5">
-        <v>4.09759855270386</v>
-      </c>
-      <c r="O5" t="s">
-        <v>21</v>
-      </c>
-      <c r="P5">
-        <v>-3.18840885162354</v>
-      </c>
-      <c r="Q5">
-        <v>203.422393798828</v>
-      </c>
-      <c r="R5">
-        <v>206.352172851563</v>
-      </c>
-      <c r="S5">
-        <v>210.206436157227</v>
-      </c>
-      <c r="T5">
-        <v>-4.13412475585938</v>
-      </c>
-      <c r="U5">
-        <v>-4.71324157714844</v>
-      </c>
-      <c r="V5">
-        <v>7.19911193847656</v>
-      </c>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B6">
-        <v>-2.6798095703125</v>
-      </c>
-      <c r="C6">
-        <v>-0.69305419921875</v>
-      </c>
-      <c r="D6">
-        <v>-3.85691833496094</v>
-      </c>
-      <c r="E6">
-        <v>202.949996948242</v>
-      </c>
-      <c r="F6">
-        <v>207.934997558594</v>
-      </c>
-      <c r="G6">
-        <v>201.940002441406</v>
-      </c>
-      <c r="H6">
-        <v>205.009994506836</v>
-      </c>
-      <c r="I6">
-        <v>207.5888671875</v>
-      </c>
-      <c r="J6">
-        <v>200.026962280273</v>
-      </c>
-      <c r="K6">
-        <v>495600</v>
-      </c>
-      <c r="L6">
-        <v>-0.752381801605225</v>
-      </c>
-      <c r="M6">
-        <v>66.2005157470703</v>
-      </c>
-      <c r="N6">
-        <v>-15.2556180953979</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="P7">
+        <v>76.2675094604492</v>
+      </c>
+      <c r="Q7">
+        <v>217.319931030273</v>
+      </c>
+      <c r="R7">
+        <v>212.919128417969</v>
+      </c>
+      <c r="S7">
+        <v>212.178527832031</v>
+      </c>
+      <c r="T7">
+        <v>-0.923660278320313</v>
+      </c>
+      <c r="U7">
+        <v>0.871368408203125</v>
+      </c>
+      <c r="V7">
+        <v>4.31997680664063</v>
+      </c>
+    </row>
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B8">
+        <v>5.10012817382813</v>
+      </c>
+      <c r="C8">
+        <v>4.27403259277344</v>
+      </c>
+      <c r="D8">
+        <v>2.93118286132813</v>
+      </c>
+      <c r="E8">
+        <v>215.899993896484</v>
+      </c>
+      <c r="F8">
+        <v>219.009994506836</v>
+      </c>
+      <c r="G8">
+        <v>214.195007324219</v>
+      </c>
+      <c r="H8">
+        <v>216.690002441406</v>
+      </c>
+      <c r="I8">
+        <v>218.19482421875</v>
+      </c>
+      <c r="J8">
+        <v>213.874847412109</v>
+      </c>
+      <c r="K8">
+        <v>672000</v>
+      </c>
+      <c r="L8">
+        <v>-0.832857429981232</v>
+      </c>
+      <c r="M8">
+        <v>20.7246761322021</v>
+      </c>
+      <c r="N8">
+        <v>-35.2244834899902</v>
+      </c>
+      <c r="O8" t="s">
         <v>1</v>
       </c>
-      <c r="P6">
-        <v>2.87883448600769</v>
-      </c>
-      <c r="Q6">
-        <v>204.37939453125</v>
-      </c>
-      <c r="R6">
-        <v>207.107116699219</v>
-      </c>
-      <c r="S6">
-        <v>211.007843017578</v>
-      </c>
-      <c r="T6">
-        <v>-0.34613037109375</v>
-      </c>
-      <c r="U6">
-        <v>-1.91304016113281</v>
-      </c>
-      <c r="V6">
-        <v>7.56190490722656</v>
-      </c>
-    </row>
-    <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="2">
-        <v>46223</v>
-      </c>
-      <c r="B7">
-        <v>-3.1585693359375</v>
-      </c>
-      <c r="C7">
-        <v>-1.64442443847656</v>
-      </c>
-      <c r="D7">
-        <v>-5.23719787597656</v>
-      </c>
-      <c r="E7">
-        <v>206.419998168945</v>
-      </c>
-      <c r="F7">
-        <v>207.949996948242</v>
-      </c>
-      <c r="G7">
-        <v>200.300003051758</v>
-      </c>
-      <c r="H7">
-        <v>201.770004272461</v>
-      </c>
-      <c r="I7">
-        <v>206.288696289063</v>
-      </c>
-      <c r="J7">
-        <v>196.926452636719</v>
-      </c>
-      <c r="K7">
-        <v>538200</v>
-      </c>
-      <c r="L7">
-        <v>-0.350001007318497</v>
-      </c>
-      <c r="M7">
-        <v>78.1178817749023</v>
-      </c>
-      <c r="N7">
-        <v>0.929085612297058</v>
-      </c>
-      <c r="O7" t="s">
-        <v>21</v>
-      </c>
-      <c r="P7">
-        <v>-53.8125686645508</v>
-      </c>
-      <c r="Q7">
-        <v>204.554290771484</v>
-      </c>
-      <c r="R7">
-        <v>207.520645141602</v>
-      </c>
-      <c r="S7">
-        <v>211.584884643555</v>
-      </c>
-      <c r="T7">
-        <v>-1.66130065917969</v>
-      </c>
-      <c r="U7">
-        <v>-3.37355041503906</v>
-      </c>
-      <c r="V7">
-        <v>9.36224365234375</v>
-      </c>
-    </row>
-    <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="2">
-        <v>46220</v>
-      </c>
-      <c r="B8">
-        <v>-0.185958862304688</v>
-      </c>
-      <c r="C8">
-        <v>-0.665054321289063</v>
-      </c>
-      <c r="D8">
-        <v>-5.76994323730469</v>
-      </c>
-      <c r="E8">
-        <v>212.990005493164</v>
-      </c>
-      <c r="F8">
-        <v>217.029998779297</v>
-      </c>
-      <c r="G8">
-        <v>204.919998168945</v>
-      </c>
-      <c r="H8">
-        <v>205.929992675781</v>
-      </c>
-      <c r="I8">
-        <v>207.690887451172</v>
-      </c>
-      <c r="J8">
-        <v>202.230224609375</v>
-      </c>
-      <c r="K8">
-        <v>349700</v>
-      </c>
-      <c r="L8">
-        <v>-0.394287109375</v>
-      </c>
-      <c r="M8">
-        <v>77.3987808227539</v>
-      </c>
-      <c r="N8">
-        <v>10.7040033340454</v>
-      </c>
-      <c r="O8" t="s">
-        <v>21</v>
-      </c>
       <c r="P8">
-        <v>-35.6265029907227</v>
+        <v>76.9874954223633</v>
       </c>
       <c r="Q8">
-        <v>207.449462890625</v>
+        <v>212.539245605469</v>
       </c>
       <c r="R8">
-        <v>209.209533691406</v>
+        <v>210.0888671875</v>
       </c>
       <c r="S8">
-        <v>212.667709350586</v>
+        <v>210.876312255859</v>
       </c>
       <c r="T8">
-        <v>-9.339111328125</v>
+        <v>-0.815170288085938</v>
       </c>
       <c r="U8">
-        <v>-2.68977355957031</v>
+        <v>-0.320159912109375</v>
       </c>
       <c r="V8">
-        <v>5.46066284179688</v>
+        <v>4.31997680664063</v>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="2">
-        <v>46219</v>
+      <c r="A9" s="1">
+        <v>46227</v>
       </c>
       <c r="B9">
-        <v>2.75093078613281</v>
+        <v>4.06655883789063</v>
       </c>
       <c r="C9">
-        <v>-0.557601928710938</v>
+        <v>1.94187927246094</v>
       </c>
       <c r="D9">
-        <v>-6.68963623046875</v>
+        <v>-0.0666046142578125</v>
       </c>
       <c r="E9">
-        <v>206.080001831055</v>
+        <v>208.380004882813</v>
       </c>
       <c r="F9">
-        <v>214.130004882813</v>
+        <v>213.690002441406</v>
       </c>
       <c r="G9">
-        <v>206.080001831055</v>
+        <v>205.800003051758</v>
       </c>
       <c r="H9">
-        <v>214</v>
+        <v>213.550003051758</v>
       </c>
       <c r="I9">
-        <v>215.233245849609</v>
+        <v>214.368743896484</v>
       </c>
       <c r="J9">
-        <v>210.91325378418</v>
+        <v>210.048736572266</v>
       </c>
       <c r="K9">
-        <v>434500</v>
+        <v>485400</v>
       </c>
       <c r="L9">
-        <v>-0.0495249442756176</v>
+        <v>-0.859048008918762</v>
       </c>
       <c r="M9">
-        <v>69.9150695800781</v>
+        <v>31.9946136474609</v>
       </c>
       <c r="N9">
-        <v>-18.2646236419678</v>
+        <v>-36.1660003662109</v>
       </c>
       <c r="O9" t="s">
         <v>1</v>
       </c>
       <c r="P9">
-        <v>49.1200866699219</v>
+        <v>56.1674270629883</v>
       </c>
       <c r="Q9">
-        <v>209.614135742188</v>
+        <v>208.829559326172</v>
       </c>
       <c r="R9">
-        <v>210.214477539063</v>
+        <v>207.952407836914</v>
       </c>
       <c r="S9">
-        <v>213.481430053711</v>
+        <v>210.00927734375</v>
       </c>
       <c r="T9">
-        <v>1.10324096679688</v>
+        <v>0.678741455078125</v>
       </c>
       <c r="U9">
-        <v>4.833251953125</v>
+        <v>4.24873352050781</v>
       </c>
       <c r="V9">
-        <v>4.31999206542969</v>
+        <v>4.32000732421875</v>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="2">
-        <v>46218</v>
+      <c r="A10" s="1">
+        <v>46226</v>
       </c>
       <c r="B10">
-        <v>-0.669586181640625</v>
+        <v>0.735427856445313</v>
       </c>
       <c r="C10">
-        <v>-3.94296264648438</v>
+        <v>-1.12678527832031</v>
       </c>
       <c r="D10">
-        <v>-9.47763061523438</v>
+        <v>-2.83802795410156</v>
       </c>
       <c r="E10">
-        <v>205.410003662109</v>
+        <v>200.570007324219</v>
       </c>
       <c r="F10">
-        <v>209.100006103516</v>
+        <v>207.524993896484</v>
       </c>
       <c r="G10">
-        <v>203.479995727539</v>
+        <v>197.789993286133</v>
       </c>
       <c r="H10">
-        <v>206.529998779297</v>
+        <v>207.110000610352</v>
       </c>
       <c r="I10">
-        <v>209.636016845703</v>
+        <v>209.162963867188</v>
       </c>
       <c r="J10">
-        <v>201.98014831543</v>
+        <v>203.450393676758</v>
       </c>
       <c r="K10">
-        <v>862000</v>
+        <v>365900</v>
       </c>
       <c r="L10">
-        <v>-0.520953238010406</v>
+        <v>-0.617619812488556</v>
       </c>
       <c r="M10">
-        <v>85.5383224487305</v>
+        <v>50.1215858459473</v>
       </c>
       <c r="N10">
-        <v>2.19319701194763</v>
+        <v>-27.2684688568115</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10">
+        <v>3.76374173164368</v>
+      </c>
+      <c r="Q10">
+        <v>204.999237060547</v>
+      </c>
+      <c r="R10">
+        <v>206.270782470703</v>
+      </c>
+      <c r="S10">
+        <v>209.638641357422</v>
+      </c>
+      <c r="T10">
+        <v>1.63796997070313</v>
+      </c>
+      <c r="U10">
+        <v>5.660400390625</v>
+      </c>
+      <c r="V10">
+        <v>5.71257019042969</v>
+      </c>
+    </row>
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B11">
+        <v>-3.04449462890625</v>
+      </c>
+      <c r="C11">
+        <v>-1.46490478515625</v>
+      </c>
+      <c r="D11">
+        <v>-3.32414245605469</v>
+      </c>
+      <c r="E11">
+        <v>206.039993286133</v>
+      </c>
+      <c r="F11">
+        <v>209.759994506836</v>
+      </c>
+      <c r="G11">
+        <v>203.139999389648</v>
+      </c>
+      <c r="H11">
+        <v>203.369995117188</v>
+      </c>
+      <c r="I11">
+        <v>205.625869750977</v>
+      </c>
+      <c r="J11">
+        <v>198.4267578125</v>
+      </c>
+      <c r="K11">
+        <v>319800</v>
+      </c>
+      <c r="L11">
+        <v>-0.9128577709198</v>
+      </c>
+      <c r="M11">
+        <v>68.9131469726563</v>
+      </c>
+      <c r="N11">
+        <v>4.09759855270386</v>
+      </c>
+      <c r="O11" t="s">
+        <v>23</v>
+      </c>
+      <c r="P11">
+        <v>-3.18840885162354</v>
+      </c>
+      <c r="Q11">
+        <v>203.422393798828</v>
+      </c>
+      <c r="R11">
+        <v>206.352172851563</v>
+      </c>
+      <c r="S11">
+        <v>210.206436157227</v>
+      </c>
+      <c r="T11">
+        <v>-4.13412475585938</v>
+      </c>
+      <c r="U11">
+        <v>-4.71324157714844</v>
+      </c>
+      <c r="V11">
+        <v>7.19911193847656</v>
+      </c>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B12">
+        <v>-2.6798095703125</v>
+      </c>
+      <c r="C12">
+        <v>-0.69305419921875</v>
+      </c>
+      <c r="D12">
+        <v>-3.85691833496094</v>
+      </c>
+      <c r="E12">
+        <v>202.949996948242</v>
+      </c>
+      <c r="F12">
+        <v>207.934997558594</v>
+      </c>
+      <c r="G12">
+        <v>201.940002441406</v>
+      </c>
+      <c r="H12">
+        <v>205.009994506836</v>
+      </c>
+      <c r="I12">
+        <v>207.5888671875</v>
+      </c>
+      <c r="J12">
+        <v>200.026962280273</v>
+      </c>
+      <c r="K12">
+        <v>495600</v>
+      </c>
+      <c r="L12">
+        <v>-0.752381801605225</v>
+      </c>
+      <c r="M12">
+        <v>66.2005157470703</v>
+      </c>
+      <c r="N12">
+        <v>-15.2556180953979</v>
+      </c>
+      <c r="O12" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>2.87883448600769</v>
+      </c>
+      <c r="Q12">
+        <v>204.37939453125</v>
+      </c>
+      <c r="R12">
+        <v>207.107116699219</v>
+      </c>
+      <c r="S12">
+        <v>211.007843017578</v>
+      </c>
+      <c r="T12">
+        <v>-0.34613037109375</v>
+      </c>
+      <c r="U12">
+        <v>-1.91304016113281</v>
+      </c>
+      <c r="V12">
+        <v>7.56190490722656</v>
+      </c>
+    </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B13">
+        <v>-3.1585693359375</v>
+      </c>
+      <c r="C13">
+        <v>-1.64442443847656</v>
+      </c>
+      <c r="D13">
+        <v>-5.23719787597656</v>
+      </c>
+      <c r="E13">
+        <v>206.419998168945</v>
+      </c>
+      <c r="F13">
+        <v>207.949996948242</v>
+      </c>
+      <c r="G13">
+        <v>200.300003051758</v>
+      </c>
+      <c r="H13">
+        <v>201.770004272461</v>
+      </c>
+      <c r="I13">
+        <v>206.288696289063</v>
+      </c>
+      <c r="J13">
+        <v>196.926452636719</v>
+      </c>
+      <c r="K13">
+        <v>538200</v>
+      </c>
+      <c r="L13">
+        <v>-0.350001007318497</v>
+      </c>
+      <c r="M13">
+        <v>78.1178817749023</v>
+      </c>
+      <c r="N13">
+        <v>0.929085612297058</v>
+      </c>
+      <c r="O13" t="s">
+        <v>23</v>
+      </c>
+      <c r="P13">
+        <v>-53.8125686645508</v>
+      </c>
+      <c r="Q13">
+        <v>204.554290771484</v>
+      </c>
+      <c r="R13">
+        <v>207.520645141602</v>
+      </c>
+      <c r="S13">
+        <v>211.584884643555</v>
+      </c>
+      <c r="T13">
+        <v>-1.66130065917969</v>
+      </c>
+      <c r="U13">
+        <v>-3.37355041503906</v>
+      </c>
+      <c r="V13">
+        <v>9.36224365234375</v>
+      </c>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B14">
+        <v>-0.185958862304688</v>
+      </c>
+      <c r="C14">
+        <v>-0.665054321289063</v>
+      </c>
+      <c r="D14">
+        <v>-5.76994323730469</v>
+      </c>
+      <c r="E14">
+        <v>212.990005493164</v>
+      </c>
+      <c r="F14">
+        <v>217.029998779297</v>
+      </c>
+      <c r="G14">
+        <v>204.919998168945</v>
+      </c>
+      <c r="H14">
+        <v>205.929992675781</v>
+      </c>
+      <c r="I14">
+        <v>207.690887451172</v>
+      </c>
+      <c r="J14">
+        <v>202.230224609375</v>
+      </c>
+      <c r="K14">
+        <v>349700</v>
+      </c>
+      <c r="L14">
+        <v>-0.394287109375</v>
+      </c>
+      <c r="M14">
+        <v>77.3987808227539</v>
+      </c>
+      <c r="N14">
+        <v>10.7040033340454</v>
+      </c>
+      <c r="O14" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14">
+        <v>-35.6265029907227</v>
+      </c>
+      <c r="Q14">
+        <v>207.449462890625</v>
+      </c>
+      <c r="R14">
+        <v>209.209533691406</v>
+      </c>
+      <c r="S14">
+        <v>212.667709350586</v>
+      </c>
+      <c r="T14">
+        <v>-9.339111328125</v>
+      </c>
+      <c r="U14">
+        <v>-2.68977355957031</v>
+      </c>
+      <c r="V14">
+        <v>5.46066284179688</v>
+      </c>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B15">
+        <v>2.75093078613281</v>
+      </c>
+      <c r="C15">
+        <v>-0.557601928710938</v>
+      </c>
+      <c r="D15">
+        <v>-6.68963623046875</v>
+      </c>
+      <c r="E15">
+        <v>206.080001831055</v>
+      </c>
+      <c r="F15">
+        <v>214.130004882813</v>
+      </c>
+      <c r="G15">
+        <v>206.080001831055</v>
+      </c>
+      <c r="H15">
+        <v>214</v>
+      </c>
+      <c r="I15">
+        <v>215.233245849609</v>
+      </c>
+      <c r="J15">
+        <v>210.91325378418</v>
+      </c>
+      <c r="K15">
+        <v>434500</v>
+      </c>
+      <c r="L15">
+        <v>-0.0495249442756176</v>
+      </c>
+      <c r="M15">
+        <v>69.9150695800781</v>
+      </c>
+      <c r="N15">
+        <v>-18.2646236419678</v>
+      </c>
+      <c r="O15" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>49.1200866699219</v>
+      </c>
+      <c r="Q15">
+        <v>209.614135742188</v>
+      </c>
+      <c r="R15">
+        <v>210.214477539063</v>
+      </c>
+      <c r="S15">
+        <v>213.481430053711</v>
+      </c>
+      <c r="T15">
+        <v>1.10324096679688</v>
+      </c>
+      <c r="U15">
+        <v>4.833251953125</v>
+      </c>
+      <c r="V15">
+        <v>4.31999206542969</v>
+      </c>
+    </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B16">
+        <v>-0.669586181640625</v>
+      </c>
+      <c r="C16">
+        <v>-3.94296264648438</v>
+      </c>
+      <c r="D16">
+        <v>-9.47763061523438</v>
+      </c>
+      <c r="E16">
+        <v>205.410003662109</v>
+      </c>
+      <c r="F16">
+        <v>209.100006103516</v>
+      </c>
+      <c r="G16">
+        <v>203.479995727539</v>
+      </c>
+      <c r="H16">
+        <v>206.529998779297</v>
+      </c>
+      <c r="I16">
+        <v>209.636016845703</v>
+      </c>
+      <c r="J16">
+        <v>201.98014831543</v>
+      </c>
+      <c r="K16">
+        <v>862000</v>
+      </c>
+      <c r="L16">
+        <v>-0.520953238010406</v>
+      </c>
+      <c r="M16">
+        <v>85.5383224487305</v>
+      </c>
+      <c r="N16">
+        <v>2.19319701194763</v>
+      </c>
+      <c r="O16" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16">
         <v>0.280125081539154</v>
       </c>
-      <c r="Q10">
+      <c r="Q16">
         <v>205.852172851563</v>
       </c>
-      <c r="R10">
+      <c r="R16">
         <v>209.189514160156</v>
       </c>
-      <c r="S10">
+      <c r="S16">
         <v>213.562515258789</v>
       </c>
-      <c r="T10">
+      <c r="T16">
         <v>0.5360107421875</v>
       </c>
-      <c r="U10">
+      <c r="U16">
         <v>-1.49984741210938</v>
       </c>
-      <c r="V10">
+      <c r="V16">
         <v>7.65586853027344</v>
       </c>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="2">
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="1">
         <v>46217</v>
       </c>
-      <c r="B11">
+      <c r="B17">
         <v>-0.71295166015625</v>
       </c>
-      <c r="C11">
+      <c r="C17">
         <v>-5.81423950195313</v>
       </c>
-      <c r="D11">
+      <c r="D17">
         <v>-10.0052185058594</v>
       </c>
-      <c r="E11">
+      <c r="E17">
         <v>208.589996337891</v>
       </c>
-      <c r="F11">
+      <c r="F17">
         <v>212.100006103516</v>
       </c>
-      <c r="G11">
+      <c r="G17">
         <v>204.100006103516</v>
       </c>
-      <c r="H11">
+      <c r="H17">
         <v>204.990005493164</v>
       </c>
-      <c r="I11">
+      <c r="I17">
         <v>207.916732788086</v>
       </c>
-      <c r="J11">
+      <c r="J17">
         <v>201.059783935547</v>
       </c>
-      <c r="K11">
+      <c r="K17">
         <v>409900</v>
       </c>
-      <c r="L11">
+      <c r="L17">
         <v>-0.790000557899475</v>
       </c>
-      <c r="M11">
+      <c r="M17">
         <v>83.7025604248047</v>
       </c>
-      <c r="N11">
+      <c r="N17">
         <v>54.0574493408203</v>
       </c>
-      <c r="O11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P11">
+      <c r="O17" t="s">
+        <v>23</v>
+      </c>
+      <c r="P17">
         <v>-20.9453811645508</v>
       </c>
-      <c r="Q11">
+      <c r="Q17">
         <v>205.657989501953</v>
       </c>
-      <c r="R11">
+      <c r="R17">
         <v>209.901092529297</v>
       </c>
-      <c r="S11">
+      <c r="S17">
         <v>214.325164794922</v>
       </c>
-      <c r="T11">
+      <c r="T17">
         <v>-4.18327331542969</v>
       </c>
-      <c r="U11">
+      <c r="U17">
         <v>-3.04022216796875</v>
       </c>
-      <c r="V11">
+      <c r="V17">
         <v>6.85694885253906</v>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="2">
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="1">
         <v>46216</v>
       </c>
-      <c r="B12">
+      <c r="B18">
         <v>-1.4044189453125</v>
       </c>
-      <c r="C12">
+      <c r="C18">
         <v>-6.99501037597656</v>
       </c>
-      <c r="D12">
+      <c r="D18">
         <v>-10.0188751220703</v>
       </c>
-      <c r="E12">
+      <c r="E18">
         <v>209.330001831055</v>
       </c>
-      <c r="F12">
+      <c r="F18">
         <v>211.380004882813</v>
       </c>
-      <c r="G12">
+      <c r="G18">
         <v>204.169998168945</v>
       </c>
-      <c r="H12">
+      <c r="H18">
         <v>205.139999389648</v>
       </c>
-      <c r="I12">
+      <c r="I18">
         <v>207.515716552734</v>
       </c>
-      <c r="J12">
+      <c r="J18">
         <v>202.215026855469</v>
       </c>
-      <c r="K12">
+      <c r="K18">
         <v>371400</v>
       </c>
-      <c r="L12">
+      <c r="L18">
         <v>-0.482381910085678</v>
       </c>
-      <c r="M12">
+      <c r="M18">
         <v>54.3320426940918</v>
       </c>
-      <c r="N12">
+      <c r="N18">
         <v>18.0216751098633</v>
       </c>
-      <c r="O12" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12">
+      <c r="O18" t="s">
+        <v>23</v>
+      </c>
+      <c r="P18">
         <v>-22.2440090179443</v>
       </c>
-      <c r="Q12">
+      <c r="Q18">
         <v>206.666961669922</v>
       </c>
-      <c r="R12">
+      <c r="R18">
         <v>211.3271484375</v>
       </c>
-      <c r="S12">
+      <c r="S18">
         <v>215.350723266602</v>
       </c>
-      <c r="T12">
+      <c r="T18">
         <v>-3.86428833007813</v>
       </c>
-      <c r="U12">
+      <c r="U18">
         <v>-1.95497131347656</v>
       </c>
-      <c r="V12">
+      <c r="V18">
         <v>5.30068969726563</v>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="2">
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="1">
         <v>46213</v>
       </c>
-      <c r="B13">
+      <c r="B19">
         <v>-1.740234375</v>
       </c>
-      <c r="C13">
+      <c r="C19">
         <v>-8.0299072265625</v>
       </c>
-      <c r="D13">
+      <c r="D19">
         <v>-9.20172119140625</v>
       </c>
-      <c r="E13">
+      <c r="E19">
         <v>207.080001831055</v>
       </c>
-      <c r="F13">
+      <c r="F19">
         <v>211.399993896484</v>
       </c>
-      <c r="G13">
+      <c r="G19">
         <v>207.080001831055</v>
       </c>
-      <c r="H13">
+      <c r="H19">
         <v>209.75</v>
       </c>
-      <c r="I13">
+      <c r="I19">
         <v>211.307601928711</v>
       </c>
-      <c r="J13">
+      <c r="J19">
         <v>206.975891113281</v>
       </c>
-      <c r="K13">
+      <c r="K19">
         <v>287200</v>
       </c>
-      <c r="L13">
+      <c r="L19">
         <v>-0.460476815700531</v>
       </c>
-      <c r="M13">
+      <c r="M19">
         <v>46.0356483459473</v>
       </c>
-      <c r="N13">
+      <c r="N19">
         <v>-7.38285160064697</v>
       </c>
-      <c r="O13" t="s">
+      <c r="O19" t="s">
         <v>1</v>
       </c>
-      <c r="P13">
+      <c r="P19">
         <v>39.6886749267578</v>
       </c>
-      <c r="Q13">
+      <c r="Q19">
         <v>208.378662109375</v>
       </c>
-      <c r="R13">
+      <c r="R19">
         <v>213.132568359375</v>
       </c>
-      <c r="S13">
+      <c r="S19">
         <v>216.684371948242</v>
       </c>
-      <c r="T13">
+      <c r="T19">
         <v>-0.0923919677734375</v>
       </c>
-      <c r="U13">
+      <c r="U19">
         <v>-0.104110717773438</v>
       </c>
-      <c r="V13">
+      <c r="V19">
         <v>4.33171081542969</v>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="2">
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="1">
         <v>46212</v>
       </c>
-      <c r="B14">
+      <c r="B20">
         <v>-6.16455078125</v>
       </c>
-      <c r="C14">
+      <c r="C20">
         <v>-10.9481964111328</v>
       </c>
-      <c r="D14">
+      <c r="D20">
         <v>-8.7427978515625</v>
       </c>
-      <c r="E14">
+      <c r="E20">
         <v>203.929992675781</v>
       </c>
-      <c r="F14">
+      <c r="F20">
         <v>207.800003051758</v>
       </c>
-      <c r="G14">
+      <c r="G20">
         <v>202.179992675781</v>
       </c>
-      <c r="H14">
+      <c r="H20">
         <v>205.619995117188</v>
       </c>
-      <c r="I14">
+      <c r="I20">
         <v>207.952926635742</v>
       </c>
-      <c r="J14">
+      <c r="J20">
         <v>201.987518310547</v>
       </c>
-      <c r="K14">
+      <c r="K20">
         <v>279800</v>
       </c>
-      <c r="L14">
+      <c r="L20">
         <v>-0.23095266520977</v>
       </c>
-      <c r="M14">
+      <c r="M20">
         <v>49.7053184509277</v>
       </c>
-      <c r="N14">
+      <c r="N20">
         <v>49.6401023864746</v>
       </c>
-      <c r="O14" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14">
+      <c r="O20" t="s">
+        <v>23</v>
+      </c>
+      <c r="P20">
         <v>-25.8721179962158</v>
       </c>
-      <c r="Q14">
+      <c r="Q20">
         <v>207.411376953125</v>
       </c>
-      <c r="R14">
+      <c r="R20">
         <v>214.041107177734</v>
       </c>
-      <c r="S14">
+      <c r="S20">
         <v>217.475799560547</v>
       </c>
-      <c r="T14">
+      <c r="T20">
         <v>0.152923583984375</v>
       </c>
-      <c r="U14">
+      <c r="U20">
         <v>-0.192474365234375</v>
       </c>
-      <c r="V14">
+      <c r="V20">
         <v>5.96540832519531</v>
       </c>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="2">
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="1">
         <v>46211</v>
       </c>
-      <c r="B15">
+      <c r="B21">
         <v>-7.58624267578125</v>
       </c>
-      <c r="C15">
+      <c r="C21">
         <v>-11.2811889648438</v>
       </c>
-      <c r="D15">
+      <c r="D21">
         <v>-7.2578125</v>
       </c>
-      <c r="E15">
+      <c r="E21">
         <v>208.119995117188</v>
       </c>
-      <c r="F15">
+      <c r="F21">
         <v>208.119995117188</v>
       </c>
-      <c r="G15">
+      <c r="G21">
         <v>201.770004272461</v>
       </c>
-      <c r="H15">
+      <c r="H21">
         <v>203.630004882813</v>
       </c>
-      <c r="I15">
+      <c r="I21">
         <v>207.301239013672</v>
       </c>
-      <c r="J15">
+      <c r="J21">
         <v>199.62126159668</v>
       </c>
-      <c r="K15">
+      <c r="K21">
         <v>425700</v>
       </c>
-      <c r="L15">
+      <c r="L21">
         <v>-0.537143528461456</v>
       </c>
-      <c r="M15">
+      <c r="M21">
         <v>33.2165756225586</v>
       </c>
-      <c r="N15">
+      <c r="N21">
         <v>-5.49726963043213</v>
       </c>
-      <c r="O15" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15">
+      <c r="O21" t="s">
+        <v>23</v>
+      </c>
+      <c r="P21">
         <v>-100</v>
       </c>
-      <c r="Q15">
+      <c r="Q21">
         <v>209.623718261719</v>
       </c>
-      <c r="R15">
+      <c r="R21">
         <v>216.522491455078</v>
       </c>
-      <c r="S15">
+      <c r="S21">
         <v>218.760314941406</v>
       </c>
-      <c r="T15">
+      <c r="T21">
         <v>-0.818756103515625</v>
       </c>
-      <c r="U15">
+      <c r="U21">
         <v>-2.14874267578125</v>
       </c>
-      <c r="V15">
+      <c r="V21">
         <v>7.67997741699219</v>
       </c>
     </row>
-    <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="2">
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="1">
         <v>46210</v>
       </c>
-      <c r="B16">
+      <c r="B22">
         <v>-4.67097473144531</v>
       </c>
-      <c r="C16">
+      <c r="C22">
         <v>-7.20199584960938</v>
       </c>
-      <c r="D16">
+      <c r="D22">
         <v>-3.62214660644531</v>
       </c>
-      <c r="E16">
+      <c r="E22">
         <v>216.729995727539</v>
       </c>
-      <c r="F16">
+      <c r="F22">
         <v>216.785003662109</v>
       </c>
-      <c r="G16">
+      <c r="G22">
         <v>211.729995727539</v>
       </c>
-      <c r="H16">
+      <c r="H22">
         <v>213.020004272461</v>
       </c>
-      <c r="I16">
+      <c r="I22">
         <v>216.423278808594</v>
       </c>
-      <c r="J16">
+      <c r="J22">
         <v>208.180236816406</v>
       </c>
-      <c r="K16">
+      <c r="K22">
         <v>447500</v>
       </c>
-      <c r="L16">
+      <c r="L22">
         <v>-0.521905779838562</v>
       </c>
-      <c r="M16">
+      <c r="M22">
         <v>35.1487998962402</v>
       </c>
-      <c r="N16">
+      <c r="N22">
         <v>24.0851993560791</v>
       </c>
-      <c r="O16" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16">
+      <c r="O22" t="s">
+        <v>23</v>
+      </c>
+      <c r="P22">
         <v>-64.1892395019531</v>
       </c>
-      <c r="Q16">
+      <c r="Q22">
         <v>215.731628417969</v>
       </c>
-      <c r="R16">
+      <c r="R22">
         <v>220.43522644043</v>
       </c>
-      <c r="S16">
+      <c r="S22">
         <v>220.59114074707</v>
       </c>
-      <c r="T16">
+      <c r="T22">
         <v>-0.361724853515625</v>
       </c>
-      <c r="U16">
+      <c r="U22">
         <v>-3.54975891113281</v>
       </c>
-      <c r="V16">
+      <c r="V22">
         <v>8.2430419921875</v>
       </c>
     </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="2">
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="1">
         <v>46209</v>
       </c>
-      <c r="B17">
+      <c r="B23">
         <v>-4.05599975585938</v>
       </c>
-      <c r="C17">
+      <c r="C23">
         <v>-5.09519958496094</v>
       </c>
-      <c r="D17">
+      <c r="D23">
         <v>-1.27426147460938</v>
       </c>
-      <c r="E17">
+      <c r="E23">
         <v>219.559997558594</v>
       </c>
-      <c r="F17">
+      <c r="F23">
         <v>221.335006713867</v>
       </c>
-      <c r="G17">
+      <c r="G23">
         <v>215.199996948242</v>
       </c>
-      <c r="H17">
+      <c r="H23">
         <v>217.539993286133</v>
       </c>
-      <c r="I17">
+      <c r="I23">
         <v>220.414031982422</v>
       </c>
-      <c r="J17">
+      <c r="J23">
         <v>212.360076904297</v>
       </c>
-      <c r="K17">
+      <c r="K23">
         <v>317400</v>
       </c>
-      <c r="L17">
+      <c r="L23">
         <v>-0.461430132389069</v>
       </c>
-      <c r="M17">
+      <c r="M23">
         <v>28.326343536377</v>
       </c>
-      <c r="N17">
+      <c r="N23">
         <v>0.00776430545374751</v>
       </c>
-      <c r="O17" t="s">
-        <v>21</v>
-      </c>
-      <c r="P17">
+      <c r="O23" t="s">
+        <v>23</v>
+      </c>
+      <c r="P23">
         <v>-34.0652503967285</v>
       </c>
-      <c r="Q17">
+      <c r="Q23">
         <v>218.923248291016</v>
       </c>
-      <c r="R17">
+      <c r="R23">
         <v>222.638076782227</v>
       </c>
-      <c r="S17">
+      <c r="S23">
         <v>221.468399047852</v>
       </c>
-      <c r="T17">
+      <c r="T23">
         <v>-0.920974731445313</v>
       </c>
-      <c r="U17">
+      <c r="U23">
         <v>-2.83992004394531</v>
       </c>
-      <c r="V17">
+      <c r="V23">
         <v>8.053955078125</v>
       </c>
     </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="2">
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="1">
         <v>46205</v>
       </c>
-      <c r="B18">
+      <c r="B24">
         <v>-5.22244262695313</v>
       </c>
-      <c r="C18">
+      <c r="C24">
         <v>-3.69883728027344</v>
       </c>
-      <c r="D18">
+      <c r="D24">
         <v>0.481735229492188</v>
       </c>
-      <c r="E18">
+      <c r="E24">
         <v>221.570007324219</v>
       </c>
-      <c r="F18">
+      <c r="F24">
         <v>224.25</v>
       </c>
-      <c r="G18">
+      <c r="G24">
         <v>217.449996948242</v>
       </c>
-      <c r="H18">
+      <c r="H24">
         <v>220.149993896484</v>
       </c>
-      <c r="I18">
+      <c r="I24">
         <v>222.696334838867</v>
       </c>
-      <c r="J18">
+      <c r="J24">
         <v>215.436553955078</v>
       </c>
-      <c r="K18">
+      <c r="K24">
         <v>315100</v>
       </c>
-      <c r="L18">
+      <c r="L24">
         <v>-0.243810743093491</v>
       </c>
-      <c r="M18">
+      <c r="M24">
         <v>28.3241443634033</v>
       </c>
-      <c r="N18">
+      <c r="N24">
         <v>-15.7467041015625</v>
       </c>
-      <c r="O18" t="s">
-        <v>21</v>
-      </c>
-      <c r="P18">
+      <c r="O24" t="s">
+        <v>23</v>
+      </c>
+      <c r="P24">
         <v>-33.757942199707</v>
       </c>
-      <c r="Q18">
+      <c r="Q24">
         <v>221.063995361328</v>
       </c>
-      <c r="R18">
+      <c r="R24">
         <v>224.132537841797</v>
       </c>
-      <c r="S18">
+      <c r="S24">
         <v>221.933364868164</v>
       </c>
-      <c r="T18">
+      <c r="T24">
         <v>-1.55366516113281</v>
       </c>
-      <c r="U18">
+      <c r="U24">
         <v>-2.01344299316406</v>
       </c>
-      <c r="V18">
+      <c r="V24">
         <v>7.25978088378906</v>
       </c>
     </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="2">
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="1">
         <v>46204</v>
       </c>
-      <c r="B19">
+      <c r="B25">
         <v>-7.31175231933594</v>
       </c>
-      <c r="C19">
+      <c r="C25">
         <v>-1.22322082519531</v>
       </c>
-      <c r="D19">
+      <c r="D25">
         <v>2.5152587890625</v>
       </c>
-      <c r="E19">
+      <c r="E25">
         <v>223.039993286133</v>
       </c>
-      <c r="F19">
+      <c r="F25">
         <v>225.330001831055</v>
       </c>
-      <c r="G19">
+      <c r="G25">
         <v>217.725006103516</v>
       </c>
-      <c r="H19">
+      <c r="H25">
         <v>219.149993896484</v>
       </c>
-      <c r="I19">
+      <c r="I25">
         <v>222.05500793457</v>
       </c>
-      <c r="J19">
+      <c r="J25">
         <v>213.670486450195</v>
       </c>
-      <c r="K19">
+      <c r="K25">
         <v>448100</v>
       </c>
-      <c r="L19">
+      <c r="L25">
         <v>-0.41142925620079</v>
       </c>
-      <c r="M19">
+      <c r="M25">
         <v>33.617847442627</v>
       </c>
-      <c r="N19">
+      <c r="N25">
         <v>51.3327713012695</v>
       </c>
-      <c r="O19" t="s">
-        <v>21</v>
-      </c>
-      <c r="P19">
+      <c r="O25" t="s">
+        <v>23</v>
+      </c>
+      <c r="P25">
         <v>-81.4012451171875</v>
       </c>
-      <c r="Q19">
+      <c r="Q25">
         <v>222.707061767578</v>
       </c>
-      <c r="R19">
+      <c r="R25">
         <v>225.312026977539</v>
       </c>
-      <c r="S19">
+      <c r="S25">
         <v>222.185882568359</v>
       </c>
-      <c r="T19">
+      <c r="T25">
         <v>-3.27499389648438</v>
       </c>
-      <c r="U19">
+      <c r="U25">
         <v>-4.05451965332031</v>
       </c>
-      <c r="V19">
+      <c r="V25">
         <v>8.384521484375</v>
       </c>
     </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="2">
+    <row r="26" ht="19.5" customHeight="1">
+      <c r="A26" s="1">
         <v>46203</v>
       </c>
-      <c r="B20">
+      <c r="B26">
         <v>-5.03436279296875</v>
       </c>
-      <c r="C20">
+      <c r="C26">
         <v>2.36578369140625</v>
       </c>
-      <c r="D20">
+      <c r="D26">
         <v>5.39582824707031</v>
       </c>
-      <c r="E20">
+      <c r="E26">
         <v>228.710006713867</v>
       </c>
-      <c r="F20">
+      <c r="F26">
         <v>228.710006713867</v>
       </c>
-      <c r="G20">
+      <c r="G26">
         <v>223.789993286133</v>
       </c>
-      <c r="H20">
+      <c r="H26">
         <v>225</v>
       </c>
-      <c r="I20">
+      <c r="I26">
         <v>228.559280395508</v>
       </c>
-      <c r="J20">
+      <c r="J26">
         <v>219.98811340332</v>
       </c>
-      <c r="K20">
+      <c r="K26">
         <v>487600</v>
       </c>
-      <c r="L20">
+      <c r="L26">
         <v>-0.147144138813019</v>
       </c>
-      <c r="M20">
+      <c r="M26">
         <v>22.2145195007324</v>
       </c>
-      <c r="N20">
+      <c r="N26">
         <v>-1.70670449733734</v>
       </c>
-      <c r="O20" t="s">
-        <v>21</v>
-      </c>
-      <c r="P20">
+      <c r="O26" t="s">
+        <v>23</v>
+      </c>
+      <c r="P26">
         <v>-53.3225021362305</v>
       </c>
-      <c r="Q20">
+      <c r="Q26">
         <v>227.120086669922</v>
       </c>
-      <c r="R20">
+      <c r="R26">
         <v>227.108779907227</v>
       </c>
-      <c r="S20">
+      <c r="S26">
         <v>222.61555480957</v>
       </c>
-      <c r="T20">
+      <c r="T26">
         <v>-0.150726318359375</v>
       </c>
-      <c r="U20">
+      <c r="U26">
         <v>-3.8018798828125</v>
       </c>
-      <c r="V20">
+      <c r="V26">
         <v>8.5711669921875</v>
       </c>
     </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="2">
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="1">
         <v>46202</v>
       </c>
-      <c r="B21">
+      <c r="B27">
         <v>-1.17393493652344</v>
       </c>
-      <c r="C21">
+      <c r="C27">
         <v>5.06808471679688</v>
       </c>
-      <c r="D21">
+      <c r="D27">
         <v>7.59321594238281</v>
       </c>
-      <c r="E21">
+      <c r="E27">
         <v>230.679992675781</v>
       </c>
-      <c r="F21">
+      <c r="F27">
         <v>234</v>
       </c>
-      <c r="G21">
+      <c r="G27">
         <v>224.270004272461</v>
       </c>
-      <c r="H21">
+      <c r="H27">
         <v>227.539993286133</v>
       </c>
-      <c r="I21">
+      <c r="I27">
         <v>229.98161315918</v>
       </c>
-      <c r="J21">
+      <c r="J27">
         <v>223.275924682617</v>
       </c>
-      <c r="K21">
+      <c r="K27">
         <v>558000</v>
       </c>
-      <c r="L21">
+      <c r="L27">
         <v>0.119046166539192</v>
       </c>
-      <c r="M21">
+      <c r="M27">
         <v>22.6002388000488</v>
       </c>
-      <c r="N21">
+      <c r="N27">
         <v>300.224365234375</v>
       </c>
-      <c r="O21" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21">
+      <c r="O27" t="s">
+        <v>23</v>
+      </c>
+      <c r="P27">
         <v>-84.3476638793945</v>
       </c>
-      <c r="Q21">
+      <c r="Q27">
         <v>229.721771240234</v>
       </c>
-      <c r="R21">
+      <c r="R27">
         <v>227.658279418945</v>
       </c>
-      <c r="S21">
+      <c r="S27">
         <v>222.285827636719</v>
       </c>
-      <c r="T21">
+      <c r="T27">
         <v>-4.01838684082031</v>
       </c>
-      <c r="U21">
+      <c r="U27">
         <v>-0.99407958984375</v>
       </c>
-      <c r="V21">
+      <c r="V27">
         <v>6.7056884765625</v>
       </c>
     </row>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="2">
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="1">
         <v>46199</v>
       </c>
-      <c r="B22">
+      <c r="B28">
         <v>4.04434204101563</v>
       </c>
-      <c r="C22">
+      <c r="C28">
         <v>7.9564208984375</v>
       </c>
-      <c r="D22">
+      <c r="D28">
         <v>9.12330627441406</v>
       </c>
-      <c r="E22">
+      <c r="E28">
         <v>234.729995727539</v>
       </c>
-      <c r="F22">
+      <c r="F28">
         <v>236.630004882813</v>
       </c>
-      <c r="G22">
+      <c r="G28">
         <v>231.25</v>
       </c>
-      <c r="H22">
+      <c r="H28">
         <v>233.830001831055</v>
       </c>
-      <c r="I22">
+      <c r="I28">
         <v>238.038299560547</v>
       </c>
-      <c r="J22">
+      <c r="J28">
         <v>228.935333251953</v>
       </c>
-      <c r="K22">
+      <c r="K28">
         <v>689400</v>
       </c>
-      <c r="L22">
+      <c r="L28">
         <v>0.502379655838013</v>
       </c>
-      <c r="M22">
+      <c r="M28">
         <v>5.64689254760742</v>
       </c>
-      <c r="N22">
+      <c r="N28">
         <v>-52.545337677002</v>
       </c>
-      <c r="O22" t="s">
+      <c r="O28" t="s">
         <v>1</v>
       </c>
-      <c r="P22">
+      <c r="P28">
         <v>18.3533096313477</v>
       </c>
-      <c r="Q22">
+      <c r="Q28">
         <v>232.512817382813</v>
       </c>
-      <c r="R22">
+      <c r="R28">
         <v>227.622451782227</v>
       </c>
-      <c r="S22">
+      <c r="S28">
         <v>221.65119934082</v>
       </c>
-      <c r="T22">
+      <c r="T28">
         <v>1.40829467773438</v>
       </c>
-      <c r="U22">
+      <c r="U28">
         <v>-2.31466674804688</v>
       </c>
-      <c r="V22">
+      <c r="V28">
         <v>9.10296630859375</v>
       </c>
     </row>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="2">
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="1">
         <v>46198</v>
       </c>
-      <c r="B23">
+      <c r="B29">
         <v>5.78359985351563</v>
       </c>
-      <c r="C23">
+      <c r="C29">
         <v>8.03373718261719</v>
       </c>
-      <c r="D23">
+      <c r="D29">
         <v>8.28437805175781</v>
       </c>
-      <c r="E23">
+      <c r="E29">
         <v>235.199996948242</v>
       </c>
-      <c r="F23">
+      <c r="F29">
         <v>245.529998779297</v>
       </c>
-      <c r="G23">
+      <c r="G29">
         <v>233.580001831055</v>
       </c>
-      <c r="H23">
+      <c r="H29">
         <v>235.440002441406</v>
       </c>
-      <c r="I23">
+      <c r="I29">
         <v>236.70881652832</v>
       </c>
-      <c r="J23">
+      <c r="J29">
         <v>233.718811035156</v>
       </c>
-      <c r="K23">
+      <c r="K29">
         <v>527600</v>
       </c>
-      <c r="L23">
+      <c r="L29">
         <v>0.828570425510406</v>
       </c>
-      <c r="M23">
+      <c r="M29">
         <v>11.8995523452759</v>
       </c>
-      <c r="N23">
+      <c r="N29">
         <v>-35.9025993347168</v>
-      </c>
-      <c r="O23" t="s">
-        <v>1</v>
-      </c>
-      <c r="P23">
-        <v>70.5036926269531</v>
-      </c>
-      <c r="Q23">
-        <v>231.421081542969</v>
-      </c>
-      <c r="R23">
-        <v>225.725662231445</v>
-      </c>
-      <c r="S23">
-        <v>220.145294189453</v>
-      </c>
-      <c r="T23">
-        <v>-8.82118225097656</v>
-      </c>
-      <c r="U23">
-        <v>0.138809204101563</v>
-      </c>
-      <c r="V23">
-        <v>2.99000549316406</v>
-      </c>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="2">
-        <v>46197</v>
-      </c>
-      <c r="B24">
-        <v>6.51521301269531</v>
-      </c>
-      <c r="C24">
-        <v>6.06591796875</v>
-      </c>
-      <c r="D24">
-        <v>5.54618835449219</v>
-      </c>
-      <c r="E24">
-        <v>223.410003662109</v>
-      </c>
-      <c r="F24">
-        <v>236.660003662109</v>
-      </c>
-      <c r="G24">
-        <v>223.410003662109</v>
-      </c>
-      <c r="H24">
-        <v>233.649993896484</v>
-      </c>
-      <c r="I24">
-        <v>235.337005615234</v>
-      </c>
-      <c r="J24">
-        <v>232.34700012207</v>
-      </c>
-      <c r="K24">
-        <v>460900</v>
-      </c>
-      <c r="L24">
-        <v>1.1047602891922</v>
-      </c>
-      <c r="M24">
-        <v>18.5647964477539</v>
-      </c>
-      <c r="N24">
-        <v>-53.7892532348633</v>
-      </c>
-      <c r="O24" t="s">
-        <v>1</v>
-      </c>
-      <c r="P24">
-        <v>80.6867752075195</v>
-      </c>
-      <c r="Q24">
-        <v>227.556564331055</v>
-      </c>
-      <c r="R24">
-        <v>222.64338684082</v>
-      </c>
-      <c r="S24">
-        <v>218.110870361328</v>
-      </c>
-      <c r="T24">
-        <v>-1.322998046875</v>
-      </c>
-      <c r="U24">
-        <v>8.93699645996094</v>
-      </c>
-      <c r="V24">
-        <v>2.99000549316406</v>
-      </c>
-    </row>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="2">
-        <v>46196</v>
-      </c>
-      <c r="B25">
-        <v>1.16447448730469</v>
-      </c>
-      <c r="C25">
-        <v>2.76557922363281</v>
-      </c>
-      <c r="D25">
-        <v>2.84368896484375</v>
-      </c>
-      <c r="E25">
-        <v>220.75</v>
-      </c>
-      <c r="F25">
-        <v>226.490005493164</v>
-      </c>
-      <c r="G25">
-        <v>219.690002441406</v>
-      </c>
-      <c r="H25">
-        <v>221.089996337891</v>
-      </c>
-      <c r="I25">
-        <v>223.436828613281</v>
-      </c>
-      <c r="J25">
-        <v>219.242706298828</v>
-      </c>
-      <c r="K25">
-        <v>358200</v>
-      </c>
-      <c r="L25">
-        <v>0.601903259754181</v>
-      </c>
-      <c r="M25">
-        <v>40.1741981506348</v>
-      </c>
-      <c r="N25">
-        <v>10.6057863235474</v>
-      </c>
-      <c r="O25" t="s">
-        <v>21</v>
-      </c>
-      <c r="P25">
-        <v>-2.53582668304443</v>
-      </c>
-      <c r="Q25">
-        <v>221.325500488281</v>
-      </c>
-      <c r="R25">
-        <v>219.562393188477</v>
-      </c>
-      <c r="S25">
-        <v>216.355331420898</v>
-      </c>
-      <c r="T25">
-        <v>-3.05317687988281</v>
-      </c>
-      <c r="U25">
-        <v>-0.447296142578125</v>
-      </c>
-      <c r="V25">
-        <v>4.19412231445313</v>
-      </c>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="2">
-        <v>46195</v>
-      </c>
-      <c r="B26">
-        <v>2.52883911132813</v>
-      </c>
-      <c r="C26">
-        <v>4.3792724609375</v>
-      </c>
-      <c r="D26">
-        <v>2.5751953125</v>
-      </c>
-      <c r="E26">
-        <v>222.800003051758</v>
-      </c>
-      <c r="F26">
-        <v>227.100692749023</v>
-      </c>
-      <c r="G26">
-        <v>221.440002441406</v>
-      </c>
-      <c r="H26">
-        <v>223.5</v>
-      </c>
-      <c r="I26">
-        <v>225.216461181641</v>
-      </c>
-      <c r="J26">
-        <v>220.324523925781</v>
-      </c>
-      <c r="K26">
-        <v>352400</v>
-      </c>
-      <c r="L26">
-        <v>0.6666659116745</v>
-      </c>
-      <c r="M26">
-        <v>36.3219680786133</v>
-      </c>
-      <c r="N26">
-        <v>-21.956018447876</v>
-      </c>
-      <c r="O26" t="s">
-        <v>1</v>
-      </c>
-      <c r="P26">
-        <v>28.0736198425293</v>
-      </c>
-      <c r="Q26">
-        <v>221.400268554688</v>
-      </c>
-      <c r="R26">
-        <v>219.206512451172</v>
-      </c>
-      <c r="S26">
-        <v>215.885971069336</v>
-      </c>
-      <c r="T26">
-        <v>-1.88423156738281</v>
-      </c>
-      <c r="U26">
-        <v>-1.115478515625</v>
-      </c>
-      <c r="V26">
-        <v>4.89193725585938</v>
-      </c>
-    </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="2">
-        <v>46191</v>
-      </c>
-      <c r="B27">
-        <v>2.8828125</v>
-      </c>
-      <c r="C27">
-        <v>3.40798950195313</v>
-      </c>
-      <c r="D27">
-        <v>0.948348999023438</v>
-      </c>
-      <c r="E27">
-        <v>214.070007324219</v>
-      </c>
-      <c r="F27">
-        <v>225.330001831055</v>
-      </c>
-      <c r="G27">
-        <v>214.070007324219</v>
-      </c>
-      <c r="H27">
-        <v>224.580001831055</v>
-      </c>
-      <c r="I27">
-        <v>226.443069458008</v>
-      </c>
-      <c r="J27">
-        <v>221.642532348633</v>
-      </c>
-      <c r="K27">
-        <v>880700</v>
-      </c>
-      <c r="L27">
-        <v>0.61714243888855</v>
-      </c>
-      <c r="M27">
-        <v>46.5403823852539</v>
-      </c>
-      <c r="N27">
-        <v>-27.2782955169678</v>
-      </c>
-      <c r="O27" t="s">
-        <v>1</v>
-      </c>
-      <c r="P27">
-        <v>33.7487487792969</v>
-      </c>
-      <c r="Q27">
-        <v>219.790908813477</v>
-      </c>
-      <c r="R27">
-        <v>217.729019165039</v>
-      </c>
-      <c r="S27">
-        <v>214.906646728516</v>
-      </c>
-      <c r="T27">
-        <v>1.11306762695313</v>
-      </c>
-      <c r="U27">
-        <v>7.57252502441406</v>
-      </c>
-      <c r="V27">
-        <v>4.800537109375</v>
-      </c>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="2">
-        <v>46190</v>
-      </c>
-      <c r="B28">
-        <v>-1.92381286621094</v>
-      </c>
-      <c r="C28">
-        <v>1.01844787597656</v>
-      </c>
-      <c r="D28">
-        <v>-0.789581298828125</v>
-      </c>
-      <c r="E28">
-        <v>218.820007324219</v>
-      </c>
-      <c r="F28">
-        <v>223.255004882813</v>
-      </c>
-      <c r="G28">
-        <v>212.820007324219</v>
-      </c>
-      <c r="H28">
-        <v>213.240005493164</v>
-      </c>
-      <c r="I28">
-        <v>216.174423217773</v>
-      </c>
-      <c r="J28">
-        <v>209.033355712891</v>
-      </c>
-      <c r="K28">
-        <v>631000</v>
-      </c>
-      <c r="L28">
-        <v>-0.11666651815176</v>
-      </c>
-      <c r="M28">
-        <v>63.9979248046875</v>
-      </c>
-      <c r="N28">
-        <v>27.7611694335938</v>
-      </c>
-      <c r="O28" t="s">
-        <v>21</v>
-      </c>
-      <c r="P28">
-        <v>-68.6583938598633</v>
-      </c>
-      <c r="Q28">
-        <v>215.361373901367</v>
-      </c>
-      <c r="R28">
-        <v>215.965225219727</v>
-      </c>
-      <c r="S28">
-        <v>213.93212890625</v>
-      </c>
-      <c r="T28">
-        <v>-7.08058166503906</v>
-      </c>
-      <c r="U28">
-        <v>-3.78665161132813</v>
-      </c>
-      <c r="V28">
-        <v>7.14106750488281</v>
-      </c>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="2">
-        <v>46189</v>
-      </c>
-      <c r="B29">
-        <v>1.97344970703125</v>
-      </c>
-      <c r="C29">
-        <v>2.63287353515625</v>
-      </c>
-      <c r="D29">
-        <v>0.584671020507813</v>
-      </c>
-      <c r="E29">
-        <v>219.720001220703</v>
-      </c>
-      <c r="F29">
-        <v>224.369995117188</v>
-      </c>
-      <c r="G29">
-        <v>218.850006103516</v>
-      </c>
-      <c r="H29">
-        <v>219.899993896484</v>
-      </c>
-      <c r="I29">
-        <v>222.829223632813</v>
-      </c>
-      <c r="J29">
-        <v>216.282592773438</v>
-      </c>
-      <c r="K29">
-        <v>511400</v>
-      </c>
-      <c r="L29">
-        <v>0.234286352992058</v>
-      </c>
-      <c r="M29">
-        <v>50.0918426513672</v>
-      </c>
-      <c r="N29">
-        <v>-3.98408317565918</v>
       </c>
       <c r="O29" t="s">
         <v>1</v>
       </c>
       <c r="P29">
-        <v>17.0568237304688</v>
+        <v>70.5036926269531</v>
       </c>
       <c r="Q29">
-        <v>217.906433105469</v>
+        <v>231.421081542969</v>
       </c>
       <c r="R29">
-        <v>216.871276855469</v>
+        <v>225.725662231445</v>
       </c>
       <c r="S29">
-        <v>214.132553100586</v>
+        <v>220.145294189453</v>
       </c>
       <c r="T29">
-        <v>-1.540771484375</v>
+        <v>-8.82118225097656</v>
       </c>
       <c r="U29">
-        <v>-2.56741333007813</v>
+        <v>0.138809204101563</v>
       </c>
       <c r="V29">
-        <v>6.546630859375</v>
+        <v>2.99000549316406</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="2">
-        <v>46188</v>
+      <c r="A30" s="1">
+        <v>46197</v>
       </c>
       <c r="B30">
-        <v>0.429031372070313</v>
+        <v>6.51521301269531</v>
       </c>
       <c r="C30">
-        <v>1.24986267089844</v>
+        <v>6.06591796875</v>
       </c>
       <c r="D30">
-        <v>0.6005859375</v>
+        <v>5.54618835449219</v>
       </c>
       <c r="E30">
-        <v>219.940002441406</v>
+        <v>223.410003662109</v>
       </c>
       <c r="F30">
-        <v>224.119995117188</v>
+        <v>236.660003662109</v>
       </c>
       <c r="G30">
-        <v>217.210006713867</v>
+        <v>223.410003662109</v>
       </c>
       <c r="H30">
-        <v>217.960006713867</v>
+        <v>233.649993896484</v>
       </c>
       <c r="I30">
-        <v>220.675964355469</v>
+        <v>235.337005615234</v>
       </c>
       <c r="J30">
-        <v>213.542007446289</v>
+        <v>232.34700012207</v>
       </c>
       <c r="K30">
-        <v>401900</v>
+        <v>460900</v>
       </c>
       <c r="L30">
-        <v>0.000953310984186828</v>
+        <v>1.1047602891922</v>
       </c>
       <c r="M30">
-        <v>52.170352935791</v>
+        <v>18.5647964477539</v>
       </c>
       <c r="N30">
-        <v>20.9181175231934</v>
+        <v>-53.7892532348633</v>
       </c>
       <c r="O30" t="s">
         <v>1</v>
       </c>
       <c r="P30">
-        <v>29.8881759643555</v>
+        <v>80.6867752075195</v>
       </c>
       <c r="Q30">
-        <v>216.145172119141</v>
+        <v>227.556564331055</v>
       </c>
       <c r="R30">
-        <v>215.803909301758</v>
+        <v>222.64338684082</v>
       </c>
       <c r="S30">
-        <v>213.501068115234</v>
+        <v>218.110870361328</v>
       </c>
       <c r="T30">
-        <v>-3.44403076171875</v>
+        <v>-1.322998046875</v>
       </c>
       <c r="U30">
-        <v>-3.66799926757813</v>
+        <v>8.93699645996094</v>
       </c>
       <c r="V30">
-        <v>7.13395690917969</v>
+        <v>2.99000549316406</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="2">
-        <v>46185</v>
+      <c r="A31" s="1">
+        <v>46196</v>
       </c>
       <c r="B31">
-        <v>1.07243347167969</v>
+        <v>1.16447448730469</v>
       </c>
       <c r="C31">
-        <v>-0.17425537109375</v>
+        <v>2.76557922363281</v>
       </c>
       <c r="D31">
-        <v>1.08833312988281</v>
+        <v>2.84368896484375</v>
       </c>
       <c r="E31">
-        <v>219.779998779297</v>
+        <v>220.75</v>
       </c>
       <c r="F31">
-        <v>222</v>
+        <v>226.490005493164</v>
       </c>
       <c r="G31">
-        <v>214.755004882813</v>
+        <v>219.690002441406</v>
       </c>
       <c r="H31">
-        <v>215.25</v>
+        <v>221.089996337891</v>
       </c>
       <c r="I31">
-        <v>217.061706542969</v>
+        <v>223.436828613281</v>
       </c>
       <c r="J31">
-        <v>211.885375976563</v>
+        <v>219.242706298828</v>
       </c>
       <c r="K31">
-        <v>379200</v>
+        <v>358200</v>
       </c>
       <c r="L31">
-        <v>0.132381618022919</v>
+        <v>0.601903259754181</v>
       </c>
       <c r="M31">
-        <v>43.145191192627</v>
+        <v>40.1741981506348</v>
       </c>
       <c r="N31">
-        <v>53.7317161560059</v>
+        <v>10.6057863235474</v>
       </c>
       <c r="O31" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P31">
-        <v>7.33034753799438</v>
+        <v>-2.53582668304443</v>
       </c>
       <c r="Q31">
-        <v>214.897262573242</v>
+        <v>221.325500488281</v>
       </c>
       <c r="R31">
-        <v>215.076751708984</v>
+        <v>219.562393188477</v>
       </c>
       <c r="S31">
-        <v>212.883346557617</v>
+        <v>216.355331420898</v>
       </c>
       <c r="T31">
-        <v>-4.93829345703125</v>
+        <v>-3.05317687988281</v>
       </c>
       <c r="U31">
-        <v>-2.86962890625</v>
+        <v>-0.447296142578125</v>
       </c>
       <c r="V31">
-        <v>5.17633056640625</v>
+        <v>4.19412231445313</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="2">
-        <v>46184</v>
+      <c r="A32" s="1">
+        <v>46195</v>
       </c>
       <c r="B32">
-        <v>2.12635803222656</v>
+        <v>2.52883911132813</v>
       </c>
       <c r="C32">
-        <v>-1.29014587402344</v>
+        <v>4.3792724609375</v>
       </c>
       <c r="D32">
-        <v>1.71394348144531</v>
+        <v>2.5751953125</v>
       </c>
       <c r="E32">
-        <v>214.199996948242</v>
+        <v>222.800003051758</v>
       </c>
       <c r="F32">
-        <v>218.270004272461</v>
+        <v>227.100692749023</v>
       </c>
       <c r="G32">
-        <v>209.860000610352</v>
+        <v>221.440002441406</v>
       </c>
       <c r="H32">
-        <v>217.059997558594</v>
+        <v>223.5</v>
       </c>
       <c r="I32">
-        <v>219.540618896484</v>
+        <v>225.216461181641</v>
       </c>
       <c r="J32">
-        <v>213.1025390625</v>
+        <v>220.324523925781</v>
       </c>
       <c r="K32">
-        <v>469000</v>
+        <v>352400</v>
       </c>
       <c r="L32">
-        <v>0.0919051393866539</v>
+        <v>0.6666659116745</v>
       </c>
       <c r="M32">
-        <v>28.0652503967285</v>
+        <v>36.3219680786133</v>
       </c>
       <c r="N32">
-        <v>-11.7517824172974</v>
+        <v>-21.956018447876</v>
       </c>
       <c r="O32" t="s">
         <v>1</v>
       </c>
       <c r="P32">
-        <v>13.5626602172852</v>
+        <v>28.0736198425293</v>
       </c>
       <c r="Q32">
-        <v>215.059967041016</v>
+        <v>221.400268554688</v>
       </c>
       <c r="R32">
-        <v>214.728973388672</v>
+        <v>219.206512451172</v>
       </c>
       <c r="S32">
-        <v>212.42985534668</v>
+        <v>215.885971069336</v>
       </c>
       <c r="T32">
-        <v>1.27061462402344</v>
+        <v>-1.88423156738281</v>
       </c>
       <c r="U32">
-        <v>3.24253845214844</v>
+        <v>-1.115478515625</v>
       </c>
       <c r="V32">
-        <v>6.43807983398438</v>
+        <v>4.89193725585938</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="2">
-        <v>46183</v>
+      <c r="A33" s="1">
+        <v>46191</v>
       </c>
       <c r="B33">
-        <v>0.013031005859375</v>
+        <v>2.8828125</v>
       </c>
       <c r="C33">
-        <v>-2.55641174316406</v>
+        <v>3.40798950195313</v>
       </c>
       <c r="D33">
-        <v>2.15742492675781</v>
+        <v>0.948348999023438</v>
       </c>
       <c r="E33">
-        <v>216.919998168945</v>
+        <v>214.070007324219</v>
       </c>
       <c r="F33">
-        <v>220.710006713867</v>
+        <v>225.330001831055</v>
       </c>
       <c r="G33">
-        <v>211.054992675781</v>
+        <v>214.070007324219</v>
       </c>
       <c r="H33">
-        <v>213.190002441406</v>
+        <v>224.580001831055</v>
       </c>
       <c r="I33">
-        <v>214.755340576172</v>
+        <v>226.443069458008</v>
       </c>
       <c r="J33">
-        <v>211.408599853516</v>
+        <v>221.642532348633</v>
       </c>
       <c r="K33">
-        <v>417900</v>
+        <v>880700</v>
       </c>
       <c r="L33">
-        <v>-0.292856842279434</v>
+        <v>0.61714243888855</v>
       </c>
       <c r="M33">
-        <v>31.8026256561279</v>
+        <v>46.5403823852539</v>
       </c>
       <c r="N33">
-        <v>36.5226135253906</v>
+        <v>-27.2782955169678</v>
       </c>
       <c r="O33" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P33">
-        <v>-5.66504573822021</v>
+        <v>33.7487487792969</v>
       </c>
       <c r="Q33">
-        <v>213.548614501953</v>
+        <v>219.790908813477</v>
       </c>
       <c r="R33">
-        <v>214.198348999023</v>
+        <v>217.729019165039</v>
       </c>
       <c r="S33">
-        <v>211.908432006836</v>
+        <v>214.906646728516</v>
       </c>
       <c r="T33">
-        <v>-5.95466613769531</v>
+        <v>1.11306762695313</v>
       </c>
       <c r="U33">
-        <v>0.353607177734375</v>
+        <v>7.57252502441406</v>
       </c>
       <c r="V33">
-        <v>3.34674072265625</v>
+        <v>4.800537109375</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="2">
-        <v>46182</v>
+      <c r="A34" s="1">
+        <v>46190</v>
       </c>
       <c r="B34">
-        <v>-0.224990844726563</v>
+        <v>-1.92381286621094</v>
       </c>
       <c r="C34">
-        <v>-2.28868103027344</v>
+        <v>1.01844787597656</v>
       </c>
       <c r="D34">
-        <v>3.43412780761719</v>
+        <v>-0.789581298828125</v>
       </c>
       <c r="E34">
-        <v>209.889999389648</v>
+        <v>218.820007324219</v>
       </c>
       <c r="F34">
-        <v>217.720001220703</v>
+        <v>223.255004882813</v>
       </c>
       <c r="G34">
-        <v>208.910003662109</v>
+        <v>212.820007324219</v>
       </c>
       <c r="H34">
-        <v>217.380004882813</v>
+        <v>213.240005493164</v>
       </c>
       <c r="I34">
-        <v>218.276824951172</v>
+        <v>216.174423217773</v>
       </c>
       <c r="J34">
-        <v>214.758758544922</v>
+        <v>209.033355712891</v>
       </c>
       <c r="K34">
-        <v>433800</v>
+        <v>631000</v>
       </c>
       <c r="L34">
-        <v>-0.356666922569275</v>
+        <v>-0.11666651815176</v>
       </c>
       <c r="M34">
-        <v>23.2947673797607</v>
+        <v>63.9979248046875</v>
       </c>
       <c r="N34">
-        <v>-34.1451034545898</v>
+        <v>27.7611694335938</v>
       </c>
       <c r="O34" t="s">
+        <v>23</v>
+      </c>
+      <c r="P34">
+        <v>-68.6583938598633</v>
+      </c>
+      <c r="Q34">
+        <v>215.361373901367</v>
+      </c>
+      <c r="R34">
+        <v>215.965225219727</v>
+      </c>
+      <c r="S34">
+        <v>213.93212890625</v>
+      </c>
+      <c r="T34">
+        <v>-7.08058166503906</v>
+      </c>
+      <c r="U34">
+        <v>-3.78665161132813</v>
+      </c>
+      <c r="V34">
+        <v>7.14106750488281</v>
+      </c>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B35">
+        <v>1.97344970703125</v>
+      </c>
+      <c r="C35">
+        <v>2.63287353515625</v>
+      </c>
+      <c r="D35">
+        <v>0.584671020507813</v>
+      </c>
+      <c r="E35">
+        <v>219.720001220703</v>
+      </c>
+      <c r="F35">
+        <v>224.369995117188</v>
+      </c>
+      <c r="G35">
+        <v>218.850006103516</v>
+      </c>
+      <c r="H35">
+        <v>219.899993896484</v>
+      </c>
+      <c r="I35">
+        <v>222.829223632813</v>
+      </c>
+      <c r="J35">
+        <v>216.282592773438</v>
+      </c>
+      <c r="K35">
+        <v>511400</v>
+      </c>
+      <c r="L35">
+        <v>0.234286352992058</v>
+      </c>
+      <c r="M35">
+        <v>50.0918426513672</v>
+      </c>
+      <c r="N35">
+        <v>-3.98408317565918</v>
+      </c>
+      <c r="O35" t="s">
         <v>1</v>
       </c>
-      <c r="P34">
-        <v>53.0890922546387</v>
-      </c>
-      <c r="Q34">
-        <v>213.970947265625</v>
-      </c>
-      <c r="R34">
-        <v>214.441665649414</v>
-      </c>
-      <c r="S34">
-        <v>211.736938476563</v>
-      </c>
-      <c r="T34">
-        <v>0.55682373046875</v>
-      </c>
-      <c r="U34">
-        <v>5.8487548828125</v>
-      </c>
-      <c r="V34">
-        <v>3.51806640625</v>
-      </c>
-    </row>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="2">
-        <v>46181</v>
-      </c>
-      <c r="B35">
-        <v>-5.31448364257813</v>
-      </c>
-      <c r="C35">
-        <v>-3.0673828125</v>
-      </c>
-      <c r="D35">
-        <v>3.69688415527344</v>
-      </c>
-      <c r="E35">
-        <v>211.529998779297</v>
-      </c>
-      <c r="F35">
-        <v>211.552505493164</v>
-      </c>
-      <c r="G35">
-        <v>206.729995727539</v>
-      </c>
-      <c r="H35">
-        <v>206.789993286133</v>
-      </c>
-      <c r="I35">
-        <v>210.649673461914</v>
-      </c>
-      <c r="J35">
-        <v>203.421966552734</v>
-      </c>
-      <c r="K35">
-        <v>475600</v>
-      </c>
-      <c r="L35">
-        <v>-0.827143371105194</v>
-      </c>
-      <c r="M35">
-        <v>35.3728713989258</v>
-      </c>
-      <c r="N35">
-        <v>-3.48923659324646</v>
-      </c>
-      <c r="O35" t="s">
-        <v>21</v>
-      </c>
       <c r="P35">
-        <v>-67.4988327026367</v>
+        <v>17.0568237304688</v>
       </c>
       <c r="Q35">
-        <v>211.1298828125</v>
+        <v>217.906433105469</v>
       </c>
       <c r="R35">
-        <v>213.676147460938</v>
+        <v>216.871276855469</v>
       </c>
       <c r="S35">
-        <v>211.021713256836</v>
+        <v>214.132553100586</v>
       </c>
       <c r="T35">
-        <v>-0.90283203125</v>
+        <v>-1.540771484375</v>
       </c>
       <c r="U35">
-        <v>-3.30802917480469</v>
+        <v>-2.56741333007813</v>
       </c>
       <c r="V35">
-        <v>7.22770690917969</v>
+        <v>6.546630859375</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="2">
-        <v>46178</v>
+      <c r="A36" s="1">
+        <v>46188</v>
       </c>
       <c r="B36">
-        <v>-3.18487548828125</v>
+        <v>0.429031372070313</v>
       </c>
       <c r="C36">
-        <v>1.36056518554688</v>
+        <v>1.24986267089844</v>
       </c>
       <c r="D36">
-        <v>6.639404296875</v>
+        <v>0.6005859375</v>
       </c>
       <c r="E36">
-        <v>216.889999389648</v>
+        <v>219.940002441406</v>
       </c>
       <c r="F36">
-        <v>218.940002441406</v>
+        <v>224.119995117188</v>
       </c>
       <c r="G36">
-        <v>210.524993896484</v>
+        <v>217.210006713867</v>
       </c>
       <c r="H36">
-        <v>212.720001220703</v>
+        <v>217.960006713867</v>
       </c>
       <c r="I36">
-        <v>215.542846679688</v>
+        <v>220.675964355469</v>
       </c>
       <c r="J36">
-        <v>210.292297363281</v>
+        <v>213.542007446289</v>
       </c>
       <c r="K36">
-        <v>428600</v>
+        <v>401900</v>
       </c>
       <c r="L36">
-        <v>-1.00380957126617</v>
+        <v>0.000953310984186828</v>
       </c>
       <c r="M36">
-        <v>36.6517372131348</v>
+        <v>52.170352935791</v>
       </c>
       <c r="N36">
-        <v>32.4399490356445</v>
+        <v>20.9181175231934</v>
       </c>
       <c r="O36" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P36">
-        <v>-44.5320930480957</v>
+        <v>29.8881759643555</v>
       </c>
       <c r="Q36">
-        <v>215.304534912109</v>
+        <v>216.145172119141</v>
       </c>
       <c r="R36">
-        <v>215.546813964844</v>
+        <v>215.803909301758</v>
       </c>
       <c r="S36">
-        <v>211.287551879883</v>
+        <v>213.501068115234</v>
       </c>
       <c r="T36">
-        <v>-3.39715576171875</v>
+        <v>-3.44403076171875</v>
       </c>
       <c r="U36">
-        <v>-0.232696533203125</v>
+        <v>-3.66799926757813</v>
       </c>
       <c r="V36">
-        <v>5.25054931640625</v>
+        <v>7.13395690917969</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="2">
-        <v>46177</v>
+      <c r="A37" s="1">
+        <v>46185</v>
       </c>
       <c r="B37">
-        <v>-1.75393676757813</v>
+        <v>1.07243347167969</v>
       </c>
       <c r="C37">
-        <v>5.22468566894531</v>
+        <v>-0.17425537109375</v>
       </c>
       <c r="D37">
-        <v>8.69973754882813</v>
+        <v>1.08833312988281</v>
       </c>
       <c r="E37">
-        <v>219.940002441406</v>
+        <v>219.779998779297</v>
       </c>
       <c r="F37">
         <v>222</v>
       </c>
       <c r="G37">
-        <v>216.309997558594</v>
+        <v>214.755004882813</v>
       </c>
       <c r="H37">
-        <v>217.5</v>
+        <v>215.25</v>
       </c>
       <c r="I37">
-        <v>219.476043701172</v>
+        <v>217.061706542969</v>
       </c>
       <c r="J37">
-        <v>214.067291259766</v>
+        <v>211.885375976563</v>
       </c>
       <c r="K37">
-        <v>295500</v>
+        <v>379200</v>
       </c>
       <c r="L37">
-        <v>-0.694285809993744</v>
+        <v>0.132381618022919</v>
       </c>
       <c r="M37">
-        <v>27.6742305755615</v>
+        <v>43.145191192627</v>
       </c>
       <c r="N37">
-        <v>-12.0971937179565</v>
+        <v>53.7317161560059</v>
       </c>
       <c r="O37" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P37">
-        <v>-8.82470893859863</v>
+        <v>7.33034753799438</v>
       </c>
       <c r="Q37">
-        <v>217.758453369141</v>
+        <v>214.897262573242</v>
       </c>
       <c r="R37">
-        <v>216.402542114258</v>
+        <v>215.076751708984</v>
       </c>
       <c r="S37">
-        <v>211.133529663086</v>
+        <v>212.883346557617</v>
       </c>
       <c r="T37">
-        <v>-2.52395629882813</v>
+        <v>-4.93829345703125</v>
       </c>
       <c r="U37">
-        <v>-2.24270629882813</v>
+        <v>-2.86962890625</v>
       </c>
       <c r="V37">
-        <v>5.40875244140625</v>
+        <v>5.17633056640625</v>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="2">
-        <v>46176</v>
+      <c r="A38" s="1">
+        <v>46184</v>
       </c>
       <c r="B38">
-        <v>-1.00196838378906</v>
+        <v>2.12635803222656</v>
       </c>
       <c r="C38">
-        <v>7.24281311035156</v>
+        <v>-1.29014587402344</v>
       </c>
       <c r="D38">
-        <v>9.52618408203125</v>
+        <v>1.71394348144531</v>
       </c>
       <c r="E38">
-        <v>215.940002441406</v>
+        <v>214.199996948242</v>
       </c>
       <c r="F38">
-        <v>220.410003662109</v>
+        <v>218.270004272461</v>
       </c>
       <c r="G38">
-        <v>215.940002441406</v>
+        <v>209.860000610352</v>
       </c>
       <c r="H38">
-        <v>218.490005493164</v>
+        <v>217.059997558594</v>
       </c>
       <c r="I38">
-        <v>221.481460571289</v>
+        <v>219.540618896484</v>
       </c>
       <c r="J38">
-        <v>215.410171508789</v>
+        <v>213.1025390625</v>
       </c>
       <c r="K38">
-        <v>312900</v>
+        <v>469000</v>
       </c>
       <c r="L38">
-        <v>-0.445714324712753</v>
+        <v>0.0919051393866539</v>
       </c>
       <c r="M38">
-        <v>31.4827613830566</v>
+        <v>28.0652503967285</v>
       </c>
       <c r="N38">
-        <v>-7.23739051818848</v>
+        <v>-11.7517824172974</v>
       </c>
       <c r="O38" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P38">
-        <v>-6.3506875038147</v>
+        <v>13.5626602172852</v>
       </c>
       <c r="Q38">
-        <v>218.502807617188</v>
+        <v>215.059967041016</v>
       </c>
       <c r="R38">
-        <v>215.883834838867</v>
+        <v>214.728973388672</v>
       </c>
       <c r="S38">
-        <v>210.299926757813</v>
+        <v>212.42985534668</v>
       </c>
       <c r="T38">
-        <v>1.07145690917969</v>
+        <v>1.27061462402344</v>
       </c>
       <c r="U38">
-        <v>-0.529830932617188</v>
+        <v>3.24253845214844</v>
       </c>
       <c r="V38">
-        <v>6.0712890625</v>
+        <v>6.43807983398438</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="2">
-        <v>46175</v>
+      <c r="A39" s="1">
+        <v>46183</v>
       </c>
       <c r="B39">
-        <v>-0.009613037109375</v>
+        <v>0.013031005859375</v>
       </c>
       <c r="C39">
-        <v>9.02542114257813</v>
+        <v>-2.55641174316406</v>
       </c>
       <c r="D39">
-        <v>9.84280395507813</v>
+        <v>2.15742492675781</v>
       </c>
       <c r="E39">
-        <v>223.220001220703</v>
+        <v>216.919998168945</v>
       </c>
       <c r="F39">
-        <v>224.089996337891</v>
+        <v>220.710006713867</v>
       </c>
       <c r="G39">
-        <v>217.529998779297</v>
+        <v>211.054992675781</v>
       </c>
       <c r="H39">
-        <v>218.279998779297</v>
+        <v>213.190002441406</v>
       </c>
       <c r="I39">
-        <v>220.592468261719</v>
+        <v>214.755340576172</v>
       </c>
       <c r="J39">
-        <v>215.267150878906</v>
+        <v>211.408599853516</v>
       </c>
       <c r="K39">
-        <v>603500</v>
+        <v>417900</v>
       </c>
       <c r="L39">
-        <v>-0.7638099193573</v>
+        <v>-0.292856842279434</v>
       </c>
       <c r="M39">
-        <v>33.9390640258789</v>
+        <v>31.8026256561279</v>
       </c>
       <c r="N39">
-        <v>-1.96039056777954</v>
+        <v>36.5226135253906</v>
       </c>
       <c r="O39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P39">
-        <v>-17.6115703582764</v>
+        <v>-5.66504573822021</v>
       </c>
       <c r="Q39">
-        <v>218.542266845703</v>
+        <v>213.548614501953</v>
       </c>
       <c r="R39">
-        <v>214.93620300293</v>
+        <v>214.198348999023</v>
       </c>
       <c r="S39">
-        <v>209.306610107422</v>
+        <v>211.908432006836</v>
       </c>
       <c r="T39">
-        <v>-3.49752807617188</v>
+        <v>-5.95466613769531</v>
       </c>
       <c r="U39">
-        <v>-2.26284790039063</v>
+        <v>0.353607177734375</v>
       </c>
       <c r="V39">
-        <v>5.3253173828125</v>
+        <v>3.34674072265625</v>
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="2">
-        <v>46174</v>
+      <c r="A40" s="1">
+        <v>46182</v>
       </c>
       <c r="B40">
-        <v>3.89060974121094</v>
+        <v>-0.224990844726563</v>
       </c>
       <c r="C40">
-        <v>10.71435546875</v>
+        <v>-2.28868103027344</v>
       </c>
       <c r="D40">
-        <v>9.41098022460938</v>
+        <v>3.43412780761719</v>
       </c>
       <c r="E40">
-        <v>219.350006103516</v>
+        <v>209.889999389648</v>
       </c>
       <c r="F40">
-        <v>223.320007324219</v>
+        <v>217.720001220703</v>
       </c>
       <c r="G40">
-        <v>215.544998168945</v>
+        <v>208.910003662109</v>
       </c>
       <c r="H40">
-        <v>221.009994506836</v>
+        <v>217.380004882813</v>
       </c>
       <c r="I40">
-        <v>223.390686035156</v>
+        <v>218.276824951172</v>
       </c>
       <c r="J40">
-        <v>218.7470703125</v>
+        <v>214.758758544922</v>
       </c>
       <c r="K40">
-        <v>384100</v>
+        <v>433800</v>
       </c>
       <c r="L40">
-        <v>-0.516666948795319</v>
+        <v>-0.356666922569275</v>
       </c>
       <c r="M40">
-        <v>34.6177062988281</v>
+        <v>23.2947673797607</v>
       </c>
       <c r="N40">
-        <v>-21.5235939025879</v>
+        <v>-34.1451034545898</v>
       </c>
       <c r="O40" t="s">
         <v>1</v>
       </c>
       <c r="P40">
-        <v>12.3044691085815</v>
+        <v>53.0890922546387</v>
       </c>
       <c r="Q40">
-        <v>219.0361328125</v>
+        <v>213.970947265625</v>
       </c>
       <c r="R40">
-        <v>213.560119628906</v>
+        <v>214.441665649414</v>
       </c>
       <c r="S40">
-        <v>208.087631225586</v>
+        <v>211.736938476563</v>
       </c>
       <c r="T40">
-        <v>0.0706787109375</v>
+        <v>0.55682373046875</v>
       </c>
       <c r="U40">
-        <v>3.20207214355469</v>
+        <v>5.8487548828125</v>
       </c>
       <c r="V40">
-        <v>4.64361572265625</v>
+        <v>3.51806640625</v>
       </c>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="2">
-        <v>46171</v>
+      <c r="A41" s="1">
+        <v>46181</v>
       </c>
       <c r="B41">
-        <v>6.86947631835938</v>
+        <v>-5.31448364257813</v>
       </c>
       <c r="C41">
-        <v>11.1900939941406</v>
+        <v>-3.0673828125</v>
       </c>
       <c r="D41">
-        <v>7.69041442871094</v>
+        <v>3.69688415527344</v>
       </c>
       <c r="E41">
-        <v>219.300003051758</v>
+        <v>211.529998779297</v>
       </c>
       <c r="F41">
-        <v>225.710006713867</v>
+        <v>211.552505493164</v>
       </c>
       <c r="G41">
-        <v>216.600006103516</v>
+        <v>206.729995727539</v>
       </c>
       <c r="H41">
-        <v>221.179992675781</v>
+        <v>206.789993286133</v>
       </c>
       <c r="I41">
-        <v>222.138717651367</v>
+        <v>210.649673461914</v>
       </c>
       <c r="J41">
-        <v>218.495803833008</v>
+        <v>203.421966552734</v>
       </c>
       <c r="K41">
-        <v>556500</v>
+        <v>475600</v>
       </c>
       <c r="L41">
-        <v>-0.495237797498703</v>
+        <v>-0.827143371105194</v>
       </c>
       <c r="M41">
-        <v>44.112247467041</v>
+        <v>35.3728713989258</v>
       </c>
       <c r="N41">
-        <v>-18.1228694915771</v>
+        <v>-3.48923659324646</v>
       </c>
       <c r="O41" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P41">
-        <v>41.0988311767578</v>
+        <v>-67.4988327026367</v>
       </c>
       <c r="Q41">
-        <v>217.030014038086</v>
+        <v>211.1298828125</v>
       </c>
       <c r="R41">
-        <v>211.236022949219</v>
+        <v>213.676147460938</v>
       </c>
       <c r="S41">
-        <v>206.59391784668</v>
+        <v>211.021713256836</v>
       </c>
       <c r="T41">
-        <v>-3.5712890625</v>
+        <v>-0.90283203125</v>
       </c>
       <c r="U41">
-        <v>1.89579772949219</v>
+        <v>-3.30802917480469</v>
       </c>
       <c r="V41">
-        <v>3.64291381835938</v>
+        <v>7.22770690917969</v>
       </c>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="2">
-        <v>46170</v>
+      <c r="A42" s="1">
+        <v>46178</v>
       </c>
       <c r="B42">
-        <v>8.15542602539063</v>
+        <v>-3.18487548828125</v>
       </c>
       <c r="C42">
-        <v>9.20321655273438</v>
+        <v>1.36056518554688</v>
       </c>
       <c r="D42">
-        <v>4.68740844726563</v>
+        <v>6.639404296875</v>
       </c>
       <c r="E42">
-        <v>214.050003051758</v>
+        <v>216.889999389648</v>
       </c>
       <c r="F42">
-        <v>220.029998779297</v>
+        <v>218.940002441406</v>
       </c>
       <c r="G42">
-        <v>211.100006103516</v>
+        <v>210.524993896484</v>
       </c>
       <c r="H42">
-        <v>218.960006713867</v>
+        <v>212.720001220703</v>
       </c>
       <c r="I42">
-        <v>219.658111572266</v>
+        <v>215.542846679688</v>
       </c>
       <c r="J42">
-        <v>216.506866455078</v>
+        <v>210.292297363281</v>
       </c>
       <c r="K42">
-        <v>304500</v>
+        <v>428600</v>
       </c>
       <c r="L42">
-        <v>-0.790237426757813</v>
+        <v>-1.00380957126617</v>
       </c>
       <c r="M42">
-        <v>53.8761520385742</v>
+        <v>36.6517372131348</v>
       </c>
       <c r="N42">
-        <v>-17.124361038208</v>
+        <v>32.4399490356445</v>
       </c>
       <c r="O42" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P42">
-        <v>67.9868469238281</v>
+        <v>-44.5320930480957</v>
       </c>
       <c r="Q42">
-        <v>213.452453613281</v>
+        <v>215.304534912109</v>
       </c>
       <c r="R42">
-        <v>208.115417480469</v>
+        <v>215.546813964844</v>
       </c>
       <c r="S42">
-        <v>204.798767089844</v>
+        <v>211.287551879883</v>
       </c>
       <c r="T42">
-        <v>-0.37188720703125</v>
+        <v>-3.39715576171875</v>
       </c>
       <c r="U42">
-        <v>5.4068603515625</v>
+        <v>-0.232696533203125</v>
       </c>
       <c r="V42">
-        <v>3.1512451171875</v>
+        <v>5.25054931640625</v>
       </c>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="2">
-        <v>46169</v>
+      <c r="A43" s="1">
+        <v>46177</v>
       </c>
       <c r="B43">
-        <v>6.98539733886719</v>
+        <v>-1.75393676757813</v>
       </c>
       <c r="C43">
-        <v>6.58055114746094</v>
+        <v>5.22468566894531</v>
       </c>
       <c r="D43">
-        <v>1.24870300292969</v>
+        <v>8.69973754882813</v>
       </c>
       <c r="E43">
-        <v>208.789993286133</v>
+        <v>219.940002441406</v>
       </c>
       <c r="F43">
-        <v>215.440002441406</v>
+        <v>222</v>
       </c>
       <c r="G43">
-        <v>208.789993286133</v>
+        <v>216.309997558594</v>
       </c>
       <c r="H43">
-        <v>214.740005493164</v>
+        <v>217.5</v>
       </c>
       <c r="I43">
-        <v>216.114059448242</v>
+        <v>219.476043701172</v>
       </c>
       <c r="J43">
-        <v>213.124053955078</v>
+        <v>214.067291259766</v>
       </c>
       <c r="K43">
-        <v>427000</v>
+        <v>295500</v>
       </c>
       <c r="L43">
-        <v>-1.16261875629425</v>
+        <v>-0.694285809993744</v>
       </c>
       <c r="M43">
-        <v>65.008430480957</v>
+        <v>27.6742305755615</v>
       </c>
       <c r="N43">
-        <v>-24.0666828155518</v>
+        <v>-12.0971937179565</v>
       </c>
       <c r="O43" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P43">
-        <v>100</v>
+        <v>-8.82470893859863</v>
       </c>
       <c r="Q43">
-        <v>208.532745361328</v>
+        <v>217.758453369141</v>
       </c>
       <c r="R43">
-        <v>204.910034179688</v>
+        <v>216.402542114258</v>
       </c>
       <c r="S43">
-        <v>203.297088623047</v>
+        <v>211.133529663086</v>
       </c>
       <c r="T43">
-        <v>0.674057006835938</v>
+        <v>-2.52395629882813</v>
       </c>
       <c r="U43">
-        <v>4.33406066894531</v>
+        <v>-2.24270629882813</v>
       </c>
       <c r="V43">
-        <v>2.99000549316406</v>
-      </c>
-    </row>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="2">
-        <v>46168</v>
-      </c>
-      <c r="B44">
-        <v>2.65672302246094</v>
-      </c>
-      <c r="C44">
-        <v>2.64399719238281</v>
-      </c>
-      <c r="D44">
-        <v>-2.11204528808594</v>
-      </c>
-      <c r="E44">
-        <v>200.520004272461</v>
-      </c>
-      <c r="F44">
-        <v>207.339996337891</v>
-      </c>
-      <c r="G44">
-        <v>200.520004272461</v>
-      </c>
-      <c r="H44">
-        <v>206.559997558594</v>
-      </c>
-      <c r="I44">
-        <v>207.45881652832</v>
-      </c>
-      <c r="J44">
-        <v>204.468811035156</v>
-      </c>
-      <c r="K44">
-        <v>353100</v>
-      </c>
-      <c r="L44">
-        <v>-1.34023833274841</v>
-      </c>
-      <c r="M44">
-        <v>85.6125259399414</v>
-      </c>
-      <c r="N44">
-        <v>-4.99024152755737</v>
-      </c>
-      <c r="O44" t="s">
-        <v>1</v>
-      </c>
-      <c r="P44">
-        <v>87.9832229614258</v>
-      </c>
-      <c r="Q44">
-        <v>202.408798217773</v>
-      </c>
-      <c r="R44">
-        <v>201.833404541016</v>
-      </c>
-      <c r="S44">
-        <v>202.026306152344</v>
-      </c>
-      <c r="T44">
-        <v>0.118820190429688</v>
-      </c>
-      <c r="U44">
-        <v>3.94880676269531</v>
-      </c>
-      <c r="V44">
-        <v>2.99000549316406</v>
+        <v>5.40875244140625</v>
       </c>
     </row>
   </sheetData>
